--- a/reports/valuation_results_2026-04-11.xlsx
+++ b/reports/valuation_results_2026-04-11.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O148"/>
+  <dimension ref="A1:O272"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -8250,6 +8250,6430 @@
         <v>151.24</v>
       </c>
     </row>
+    <row r="149">
+      <c r="A149" s="1" t="inlineStr">
+        <is>
+          <t>011210</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>현대위아</t>
+        </is>
+      </c>
+      <c r="C149" s="3" t="n">
+        <v>78800</v>
+      </c>
+      <c r="D149" s="3" t="n">
+        <v>107279.58</v>
+      </c>
+      <c r="E149" s="2" t="n">
+        <v>-26.55</v>
+      </c>
+      <c r="F149" s="2" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="G149" s="2" t="n">
+        <v>10.86</v>
+      </c>
+      <c r="H149" s="2" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="I149" s="2" t="n">
+        <v>21.89</v>
+      </c>
+      <c r="J149" s="2" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="K149" s="2" t="n">
+        <v>15.19</v>
+      </c>
+      <c r="L149" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M149" s="2" t="inlineStr">
+        <is>
+          <t>저평가</t>
+        </is>
+      </c>
+      <c r="N149" s="4" t="n">
+        <v>-6.58</v>
+      </c>
+      <c r="O149" s="4" t="n">
+        <v>261.77</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="5" t="inlineStr">
+        <is>
+          <t>192820</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>코스맥스</t>
+        </is>
+      </c>
+      <c r="C150" s="6" t="n">
+        <v>186700</v>
+      </c>
+      <c r="D150" s="6" t="n">
+        <v>185740.02</v>
+      </c>
+      <c r="E150" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="F150" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="G150" t="n">
+        <v>14.87</v>
+      </c>
+      <c r="H150" t="n">
+        <v>23.22</v>
+      </c>
+      <c r="I150" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="J150" t="n">
+        <v>20.62</v>
+      </c>
+      <c r="K150" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="L150" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>적정</t>
+        </is>
+      </c>
+      <c r="N150" s="7" t="n">
+        <v>11.63</v>
+      </c>
+      <c r="O150" s="7" t="n">
+        <v>237.01</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="1" t="inlineStr">
+        <is>
+          <t>005440</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>현대지에프홀딩스</t>
+        </is>
+      </c>
+      <c r="C151" s="3" t="n">
+        <v>13530</v>
+      </c>
+      <c r="D151" s="3" t="n">
+        <v>22901.25</v>
+      </c>
+      <c r="E151" s="2" t="n">
+        <v>-40.92</v>
+      </c>
+      <c r="F151" s="2" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="G151" s="2" t="n">
+        <v>6.36</v>
+      </c>
+      <c r="H151" s="2" t="n">
+        <v>7.79</v>
+      </c>
+      <c r="I151" s="2" t="n">
+        <v>9.859999999999999</v>
+      </c>
+      <c r="J151" s="2" t="n">
+        <v>6.44</v>
+      </c>
+      <c r="K151" s="2" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="L151" s="2" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="M151" s="2" t="inlineStr">
+        <is>
+          <t>저평가</t>
+        </is>
+      </c>
+      <c r="N151" s="4" t="n">
+        <v>38.36</v>
+      </c>
+      <c r="O151" s="4" t="n">
+        <v>158.58</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="5" t="inlineStr">
+        <is>
+          <t>067310</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>하나마이크론</t>
+        </is>
+      </c>
+      <c r="C152" s="6" t="n">
+        <v>31000</v>
+      </c>
+      <c r="D152" s="6" t="n">
+        <v>27568.82</v>
+      </c>
+      <c r="E152" t="n">
+        <v>12.45</v>
+      </c>
+      <c r="F152" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="G152" t="n">
+        <v>20.33</v>
+      </c>
+      <c r="H152" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="I152" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="J152" t="n">
+        <v>26.98</v>
+      </c>
+      <c r="K152" t="n">
+        <v>17.35</v>
+      </c>
+      <c r="L152" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>고평가</t>
+        </is>
+      </c>
+      <c r="N152" s="7" t="n">
+        <v>19.57</v>
+      </c>
+      <c r="O152" s="7" t="n">
+        <v>187.61</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="5" t="inlineStr">
+        <is>
+          <t>082920</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>비츠로셀</t>
+        </is>
+      </c>
+      <c r="C153" s="6" t="n">
+        <v>45250</v>
+      </c>
+      <c r="D153" s="6" t="n">
+        <v>23277.64</v>
+      </c>
+      <c r="E153" t="n">
+        <v>94.39</v>
+      </c>
+      <c r="F153" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="G153" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="H153" t="n">
+        <v>20.25</v>
+      </c>
+      <c r="I153" t="n">
+        <v>19.17</v>
+      </c>
+      <c r="J153" t="n">
+        <v>18.36</v>
+      </c>
+      <c r="K153" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L153" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>고평가</t>
+        </is>
+      </c>
+      <c r="N153" s="7" t="n">
+        <v>33.53</v>
+      </c>
+      <c r="O153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="5" t="inlineStr">
+        <is>
+          <t>039200</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>오스코텍</t>
+        </is>
+      </c>
+      <c r="C154" s="6" t="n">
+        <v>53000</v>
+      </c>
+      <c r="D154" s="6" t="n">
+        <v>29906.07</v>
+      </c>
+      <c r="E154" t="n">
+        <v>77.22</v>
+      </c>
+      <c r="F154" t="n">
+        <v>10.72</v>
+      </c>
+      <c r="G154" t="n">
+        <v>83.53</v>
+      </c>
+      <c r="H154" t="n">
+        <v>13.03</v>
+      </c>
+      <c r="I154" t="n">
+        <v>296.01</v>
+      </c>
+      <c r="J154" t="n">
+        <v>51.33</v>
+      </c>
+      <c r="K154" t="n">
+        <v>210.28</v>
+      </c>
+      <c r="L154" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>고평가</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr"/>
+      <c r="O154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="5" t="inlineStr">
+        <is>
+          <t>475150</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>SK이터닉스</t>
+        </is>
+      </c>
+      <c r="C155" s="6" t="n">
+        <v>59000</v>
+      </c>
+      <c r="D155" s="6" t="n">
+        <v>53195.15</v>
+      </c>
+      <c r="E155" t="n">
+        <v>10.91</v>
+      </c>
+      <c r="F155" t="n">
+        <v>6.44</v>
+      </c>
+      <c r="G155" t="n">
+        <v>48.77</v>
+      </c>
+      <c r="H155" t="n">
+        <v>14.06</v>
+      </c>
+      <c r="I155" t="n">
+        <v>43.96</v>
+      </c>
+      <c r="J155" t="n">
+        <v>13.61</v>
+      </c>
+      <c r="K155" t="n">
+        <v>26.74</v>
+      </c>
+      <c r="L155" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>고평가</t>
+        </is>
+      </c>
+      <c r="N155" s="7" t="n">
+        <v>209.09</v>
+      </c>
+      <c r="O155" s="7" t="n">
+        <v>-58.02</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="1" t="inlineStr">
+        <is>
+          <t>298020</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>효성티앤씨</t>
+        </is>
+      </c>
+      <c r="C156" s="3" t="n">
+        <v>464000</v>
+      </c>
+      <c r="D156" s="3" t="n">
+        <v>576635.42</v>
+      </c>
+      <c r="E156" s="2" t="n">
+        <v>-19.53</v>
+      </c>
+      <c r="F156" s="2" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="G156" s="2" t="n">
+        <v>13.83</v>
+      </c>
+      <c r="H156" s="2" t="n">
+        <v>8.92</v>
+      </c>
+      <c r="I156" s="2" t="n">
+        <v>28.88</v>
+      </c>
+      <c r="J156" s="2" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="K156" s="2" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="L156" s="2" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="M156" s="2" t="inlineStr">
+        <is>
+          <t>저평가</t>
+        </is>
+      </c>
+      <c r="N156" s="4" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="O156" s="4" t="n">
+        <v>3.41</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="5" t="inlineStr">
+        <is>
+          <t>008770</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>호텔신라</t>
+        </is>
+      </c>
+      <c r="C157" s="6" t="n">
+        <v>50100</v>
+      </c>
+      <c r="D157" s="6" t="n">
+        <v>38650.23</v>
+      </c>
+      <c r="E157" t="n">
+        <v>29.62</v>
+      </c>
+      <c r="F157" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G157" t="n">
+        <v>25.98</v>
+      </c>
+      <c r="H157" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="I157" t="n">
+        <v>65.02</v>
+      </c>
+      <c r="J157" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="K157" t="n">
+        <v>49.92</v>
+      </c>
+      <c r="L157" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>고평가</t>
+        </is>
+      </c>
+      <c r="N157" t="inlineStr"/>
+      <c r="O157" s="7" t="n">
+        <v>-73.91</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="1" t="inlineStr">
+        <is>
+          <t>089030</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>테크윙</t>
+        </is>
+      </c>
+      <c r="C158" s="3" t="n">
+        <v>53000</v>
+      </c>
+      <c r="D158" s="3" t="n">
+        <v>89958.82000000001</v>
+      </c>
+      <c r="E158" s="2" t="n">
+        <v>-41.08</v>
+      </c>
+      <c r="F158" s="2" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="G158" s="2" t="n">
+        <v>26.82</v>
+      </c>
+      <c r="H158" s="2" t="n">
+        <v>30.36</v>
+      </c>
+      <c r="I158" s="2" t="n">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="J158" s="2" t="n">
+        <v>41.24</v>
+      </c>
+      <c r="K158" s="2" t="n">
+        <v>27.08</v>
+      </c>
+      <c r="L158" s="2" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="M158" s="2" t="inlineStr">
+        <is>
+          <t>저평가</t>
+        </is>
+      </c>
+      <c r="N158" s="4" t="n">
+        <v>55.56</v>
+      </c>
+      <c r="O158" s="4" t="n">
+        <v>-89.23</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="5" t="inlineStr">
+        <is>
+          <t>078600</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>대주전자재료</t>
+        </is>
+      </c>
+      <c r="C159" s="6" t="n">
+        <v>123800</v>
+      </c>
+      <c r="D159" s="6" t="n">
+        <v>44639.27</v>
+      </c>
+      <c r="E159" t="n">
+        <v>177.33</v>
+      </c>
+      <c r="F159" t="n">
+        <v>6.46</v>
+      </c>
+      <c r="G159" t="n">
+        <v>59.82</v>
+      </c>
+      <c r="H159" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="I159" t="n">
+        <v>40.43</v>
+      </c>
+      <c r="J159" t="n">
+        <v>14.83</v>
+      </c>
+      <c r="K159" t="n">
+        <v>25.91</v>
+      </c>
+      <c r="L159" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>고평가</t>
+        </is>
+      </c>
+      <c r="N159" s="7" t="n">
+        <v>-29.59</v>
+      </c>
+      <c r="O159" s="7" t="n">
+        <v>183.56</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="5" t="inlineStr">
+        <is>
+          <t>007810</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>코리아써키트</t>
+        </is>
+      </c>
+      <c r="C160" s="6" t="n">
+        <v>80100</v>
+      </c>
+      <c r="D160" s="6" t="n">
+        <v>86195.28</v>
+      </c>
+      <c r="E160" t="n">
+        <v>-7.07</v>
+      </c>
+      <c r="F160" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="G160" t="n">
+        <v>21.71</v>
+      </c>
+      <c r="H160" t="n">
+        <v>21.28</v>
+      </c>
+      <c r="I160" t="n">
+        <v>37.04</v>
+      </c>
+      <c r="J160" t="n">
+        <v>26.45</v>
+      </c>
+      <c r="K160" t="n">
+        <v>10.34</v>
+      </c>
+      <c r="L160" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>적정</t>
+        </is>
+      </c>
+      <c r="N160" t="inlineStr"/>
+      <c r="O160" s="7" t="n">
+        <v>81.14</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="5" t="inlineStr">
+        <is>
+          <t>322000</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>HD현대에너지솔루션</t>
+        </is>
+      </c>
+      <c r="C161" s="6" t="n">
+        <v>168400</v>
+      </c>
+      <c r="D161" s="6" t="n">
+        <v>134261.93</v>
+      </c>
+      <c r="E161" t="n">
+        <v>25.43</v>
+      </c>
+      <c r="F161" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="G161" t="n">
+        <v>27.25</v>
+      </c>
+      <c r="H161" t="n">
+        <v>15.02</v>
+      </c>
+      <c r="I161" t="n">
+        <v>35.71</v>
+      </c>
+      <c r="J161" t="n">
+        <v>21</v>
+      </c>
+      <c r="K161" t="n">
+        <v>14.71</v>
+      </c>
+      <c r="L161" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>고평가</t>
+        </is>
+      </c>
+      <c r="N161" t="inlineStr"/>
+      <c r="O161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="5" t="inlineStr">
+        <is>
+          <t>098460</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>고영</t>
+        </is>
+      </c>
+      <c r="C162" s="6" t="n">
+        <v>27350</v>
+      </c>
+      <c r="D162" s="6" t="n">
+        <v>22200.53</v>
+      </c>
+      <c r="E162" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="F162" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="G162" t="n">
+        <v>47.87</v>
+      </c>
+      <c r="H162" t="n">
+        <v>11.41</v>
+      </c>
+      <c r="I162" t="n">
+        <v>40.64</v>
+      </c>
+      <c r="J162" t="n">
+        <v>11.91</v>
+      </c>
+      <c r="K162" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="L162" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>고평가</t>
+        </is>
+      </c>
+      <c r="N162" s="7" t="n">
+        <v>84.38</v>
+      </c>
+      <c r="O162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="1" t="inlineStr">
+        <is>
+          <t>161890</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>한국콜마</t>
+        </is>
+      </c>
+      <c r="C163" s="3" t="n">
+        <v>78900</v>
+      </c>
+      <c r="D163" s="3" t="n">
+        <v>87944.33</v>
+      </c>
+      <c r="E163" s="2" t="n">
+        <v>-10.28</v>
+      </c>
+      <c r="F163" s="2" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="G163" s="2" t="n">
+        <v>12.62</v>
+      </c>
+      <c r="H163" s="2" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="I163" s="2" t="n">
+        <v>19.25</v>
+      </c>
+      <c r="J163" s="2" t="n">
+        <v>14.87</v>
+      </c>
+      <c r="K163" s="2" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="L163" s="2" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="M163" s="2" t="inlineStr">
+        <is>
+          <t>저평가</t>
+        </is>
+      </c>
+      <c r="N163" s="4" t="n">
+        <v>23.57</v>
+      </c>
+      <c r="O163" s="4" t="n">
+        <v>276.73</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="1" t="inlineStr">
+        <is>
+          <t>007070</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>GS리테일</t>
+        </is>
+      </c>
+      <c r="C164" s="3" t="n">
+        <v>22150</v>
+      </c>
+      <c r="D164" s="3" t="n">
+        <v>29435.01</v>
+      </c>
+      <c r="E164" s="2" t="n">
+        <v>-24.75</v>
+      </c>
+      <c r="F164" s="2" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="G164" s="2" t="n">
+        <v>9.41</v>
+      </c>
+      <c r="H164" s="2" t="n">
+        <v>5.96</v>
+      </c>
+      <c r="I164" s="2" t="n">
+        <v>11.15</v>
+      </c>
+      <c r="J164" s="2" t="n">
+        <v>5.39</v>
+      </c>
+      <c r="K164" s="2" t="n">
+        <v>6.38</v>
+      </c>
+      <c r="L164" s="2" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="M164" s="2" t="inlineStr">
+        <is>
+          <t>저평가</t>
+        </is>
+      </c>
+      <c r="N164" s="4" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="O164" s="4" t="n">
+        <v>7.28</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="1" t="inlineStr">
+        <is>
+          <t>001120</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>LX인터내셔널</t>
+        </is>
+      </c>
+      <c r="C165" s="3" t="n">
+        <v>47400</v>
+      </c>
+      <c r="D165" s="3" t="n">
+        <v>83001.39</v>
+      </c>
+      <c r="E165" s="2" t="n">
+        <v>-42.89</v>
+      </c>
+      <c r="F165" s="2" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="G165" s="2" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="H165" s="2" t="n">
+        <v>9.52</v>
+      </c>
+      <c r="I165" s="2" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="J165" s="2" t="n">
+        <v>6.77</v>
+      </c>
+      <c r="K165" s="2" t="n">
+        <v>-5.25</v>
+      </c>
+      <c r="L165" s="2" t="inlineStr"/>
+      <c r="M165" s="2" t="inlineStr">
+        <is>
+          <t>저평가</t>
+        </is>
+      </c>
+      <c r="N165" s="4" t="n">
+        <v>-40.27</v>
+      </c>
+      <c r="O165" s="4" t="n">
+        <v>240.96</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="1" t="inlineStr">
+        <is>
+          <t>069960</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>현대백화점</t>
+        </is>
+      </c>
+      <c r="C166" s="3" t="n">
+        <v>80900</v>
+      </c>
+      <c r="D166" s="3" t="n">
+        <v>169509.38</v>
+      </c>
+      <c r="E166" s="2" t="n">
+        <v>-52.27</v>
+      </c>
+      <c r="F166" s="2" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="G166" s="2" t="n">
+        <v>7.28</v>
+      </c>
+      <c r="H166" s="2" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="I166" s="2" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="J166" s="2" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="K166" s="2" t="n">
+        <v>15.24</v>
+      </c>
+      <c r="L166" s="2" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="M166" s="2" t="inlineStr">
+        <is>
+          <t>저평가</t>
+        </is>
+      </c>
+      <c r="N166" s="4" t="n">
+        <v>33.06</v>
+      </c>
+      <c r="O166" s="4" t="n">
+        <v>240.76</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="1" t="inlineStr">
+        <is>
+          <t>073240</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>금호타이어</t>
+        </is>
+      </c>
+      <c r="C167" s="3" t="n">
+        <v>6190</v>
+      </c>
+      <c r="D167" s="3" t="n">
+        <v>16428.67</v>
+      </c>
+      <c r="E167" s="2" t="n">
+        <v>-62.32</v>
+      </c>
+      <c r="F167" s="2" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G167" s="2" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="H167" s="2" t="n">
+        <v>19.11</v>
+      </c>
+      <c r="I167" s="2" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="J167" s="2" t="n">
+        <v>14.59</v>
+      </c>
+      <c r="K167" s="2" t="n">
+        <v>-12.93</v>
+      </c>
+      <c r="L167" s="2" t="inlineStr"/>
+      <c r="M167" s="2" t="inlineStr">
+        <is>
+          <t>저평가</t>
+        </is>
+      </c>
+      <c r="N167" s="4" t="n">
+        <v>-2.16</v>
+      </c>
+      <c r="O167" s="4" t="n">
+        <v>326.28</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="1" t="inlineStr">
+        <is>
+          <t>069620</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>대웅제약</t>
+        </is>
+      </c>
+      <c r="C168" s="3" t="n">
+        <v>150400</v>
+      </c>
+      <c r="D168" s="3" t="n">
+        <v>276210.15</v>
+      </c>
+      <c r="E168" s="2" t="n">
+        <v>-45.55</v>
+      </c>
+      <c r="F168" s="2" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="G168" s="2" t="n">
+        <v>10.64</v>
+      </c>
+      <c r="H168" s="2" t="n">
+        <v>14.93</v>
+      </c>
+      <c r="I168" s="2" t="n">
+        <v>20.09</v>
+      </c>
+      <c r="J168" s="2" t="n">
+        <v>16.39</v>
+      </c>
+      <c r="K168" s="2" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="L168" s="2" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="M168" s="2" t="inlineStr">
+        <is>
+          <t>저평가</t>
+        </is>
+      </c>
+      <c r="N168" s="4" t="n">
+        <v>14.21</v>
+      </c>
+      <c r="O168" s="4" t="n">
+        <v>-1.56</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="5" t="inlineStr">
+        <is>
+          <t>290650</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>엘앤씨바이오</t>
+        </is>
+      </c>
+      <c r="C169" s="6" t="n">
+        <v>69700</v>
+      </c>
+      <c r="D169" s="6" t="n">
+        <v>26493.98</v>
+      </c>
+      <c r="E169" t="n">
+        <v>163.08</v>
+      </c>
+      <c r="F169" t="n">
+        <v>6.84</v>
+      </c>
+      <c r="G169" t="n">
+        <v>144.99</v>
+      </c>
+      <c r="H169" t="n">
+        <v>5.19</v>
+      </c>
+      <c r="I169" t="n">
+        <v>375.06</v>
+      </c>
+      <c r="J169" t="n">
+        <v>59.59</v>
+      </c>
+      <c r="K169" t="n">
+        <v>242.58</v>
+      </c>
+      <c r="L169" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>고평가</t>
+        </is>
+      </c>
+      <c r="N169" s="7" t="n">
+        <v>12.82</v>
+      </c>
+      <c r="O169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="1" t="inlineStr">
+        <is>
+          <t>006040</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>동원산업</t>
+        </is>
+      </c>
+      <c r="C170" s="3" t="n">
+        <v>38500</v>
+      </c>
+      <c r="D170" s="3" t="n">
+        <v>83410.06</v>
+      </c>
+      <c r="E170" s="2" t="n">
+        <v>-53.84</v>
+      </c>
+      <c r="F170" s="2" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="G170" s="2" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="H170" s="2" t="n">
+        <v>8.85</v>
+      </c>
+      <c r="I170" s="2" t="n">
+        <v>11.66</v>
+      </c>
+      <c r="J170" s="2" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="K170" s="2" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="L170" s="2" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="M170" s="2" t="inlineStr">
+        <is>
+          <t>저평가</t>
+        </is>
+      </c>
+      <c r="N170" s="4" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="O170" s="4" t="n">
+        <v>283.15</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="5" t="inlineStr">
+        <is>
+          <t>006280</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>녹십자</t>
+        </is>
+      </c>
+      <c r="C171" s="6" t="n">
+        <v>144300</v>
+      </c>
+      <c r="D171" s="6" t="n">
+        <v>113121.33</v>
+      </c>
+      <c r="E171" t="n">
+        <v>27.56</v>
+      </c>
+      <c r="F171" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G171" t="n">
+        <v>37.89</v>
+      </c>
+      <c r="H171" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="I171" t="n">
+        <v>45.34</v>
+      </c>
+      <c r="J171" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="K171" t="n">
+        <v>40.67</v>
+      </c>
+      <c r="L171" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>고평가</t>
+        </is>
+      </c>
+      <c r="N171" s="7" t="n">
+        <v>115.26</v>
+      </c>
+      <c r="O171" s="7" t="n">
+        <v>366.89</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="5" t="inlineStr">
+        <is>
+          <t>099320</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>쎄트렉아이</t>
+        </is>
+      </c>
+      <c r="C172" s="6" t="n">
+        <v>150800</v>
+      </c>
+      <c r="D172" s="6" t="n">
+        <v>33440.16</v>
+      </c>
+      <c r="E172" t="n">
+        <v>350.95</v>
+      </c>
+      <c r="F172" t="n">
+        <v>6.63</v>
+      </c>
+      <c r="G172" t="n">
+        <v>98.7</v>
+      </c>
+      <c r="H172" t="n">
+        <v>6.89</v>
+      </c>
+      <c r="I172" t="n">
+        <v>32.32</v>
+      </c>
+      <c r="J172" t="n">
+        <v>7.19</v>
+      </c>
+      <c r="K172" t="n">
+        <v>24.53</v>
+      </c>
+      <c r="L172" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>고평가</t>
+        </is>
+      </c>
+      <c r="N172" s="7" t="n">
+        <v>105.88</v>
+      </c>
+      <c r="O172" s="7" t="n">
+        <v>-12.5</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="5" t="inlineStr">
+        <is>
+          <t>100090</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>SK오션플랜트</t>
+        </is>
+      </c>
+      <c r="C173" s="6" t="n">
+        <v>25750</v>
+      </c>
+      <c r="D173" s="6" t="n">
+        <v>22099.61</v>
+      </c>
+      <c r="E173" t="n">
+        <v>16.52</v>
+      </c>
+      <c r="F173" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="G173" t="n">
+        <v>31.54</v>
+      </c>
+      <c r="H173" t="n">
+        <v>6.19</v>
+      </c>
+      <c r="I173" t="n">
+        <v>51.54</v>
+      </c>
+      <c r="J173" t="n">
+        <v>9.140000000000001</v>
+      </c>
+      <c r="K173" t="n">
+        <v>43.78</v>
+      </c>
+      <c r="L173" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>고평가</t>
+        </is>
+      </c>
+      <c r="N173" s="7" t="n">
+        <v>38.18</v>
+      </c>
+      <c r="O173" s="7" t="n">
+        <v>26.67</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="5" t="inlineStr">
+        <is>
+          <t>232140</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>와이씨</t>
+        </is>
+      </c>
+      <c r="C174" s="6" t="n">
+        <v>19500</v>
+      </c>
+      <c r="D174" s="6" t="n">
+        <v>13948.12</v>
+      </c>
+      <c r="E174" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="F174" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="G174" t="n">
+        <v>46.84</v>
+      </c>
+      <c r="H174" t="n">
+        <v>8.27</v>
+      </c>
+      <c r="I174" t="n">
+        <v>36.36</v>
+      </c>
+      <c r="J174" t="n">
+        <v>10.86</v>
+      </c>
+      <c r="K174" t="n">
+        <v>24.91</v>
+      </c>
+      <c r="L174" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>고평가</t>
+        </is>
+      </c>
+      <c r="N174" s="7" t="n">
+        <v>60.38</v>
+      </c>
+      <c r="O174" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="1" t="inlineStr">
+        <is>
+          <t>095610</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>테스</t>
+        </is>
+      </c>
+      <c r="C175" s="3" t="n">
+        <v>82500</v>
+      </c>
+      <c r="D175" s="3" t="n">
+        <v>125811</v>
+      </c>
+      <c r="E175" s="2" t="n">
+        <v>-34.43</v>
+      </c>
+      <c r="F175" s="2" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="G175" s="2" t="n">
+        <v>18.57</v>
+      </c>
+      <c r="H175" s="2" t="n">
+        <v>18.67</v>
+      </c>
+      <c r="I175" s="2" t="n">
+        <v>23.82</v>
+      </c>
+      <c r="J175" s="2" t="n">
+        <v>16.75</v>
+      </c>
+      <c r="K175" s="2" t="n">
+        <v>6.96</v>
+      </c>
+      <c r="L175" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="M175" s="2" t="inlineStr">
+        <is>
+          <t>저평가</t>
+        </is>
+      </c>
+      <c r="N175" s="4" t="n">
+        <v>25.77</v>
+      </c>
+      <c r="O175" s="4" t="n">
+        <v>4.59</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="5" t="inlineStr">
+        <is>
+          <t>060370</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>LS마린솔루션</t>
+        </is>
+      </c>
+      <c r="C176" s="6" t="n">
+        <v>29550</v>
+      </c>
+      <c r="D176" s="6" t="n">
+        <v>7747.41</v>
+      </c>
+      <c r="E176" t="n">
+        <v>281.42</v>
+      </c>
+      <c r="F176" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="G176" t="n">
+        <v>116.64</v>
+      </c>
+      <c r="H176" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="I176" t="n">
+        <v>161.35</v>
+      </c>
+      <c r="J176" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="K176" t="n">
+        <v>162.44</v>
+      </c>
+      <c r="L176" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>고평가</t>
+        </is>
+      </c>
+      <c r="N176" s="7" t="n">
+        <v>-70</v>
+      </c>
+      <c r="O176" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="1" t="inlineStr">
+        <is>
+          <t>294870</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>IPARK현대산업개발</t>
+        </is>
+      </c>
+      <c r="C177" s="3" t="n">
+        <v>22750</v>
+      </c>
+      <c r="D177" s="3" t="n">
+        <v>211818.96</v>
+      </c>
+      <c r="E177" s="2" t="n">
+        <v>-89.26000000000001</v>
+      </c>
+      <c r="F177" s="2" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="G177" s="2" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="H177" s="2" t="n">
+        <v>10.05</v>
+      </c>
+      <c r="I177" s="2" t="n">
+        <v>39.15</v>
+      </c>
+      <c r="J177" s="2" t="n">
+        <v>10.74</v>
+      </c>
+      <c r="K177" s="2" t="n">
+        <v>26.77</v>
+      </c>
+      <c r="L177" s="2" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="M177" s="2" t="inlineStr">
+        <is>
+          <t>저평가</t>
+        </is>
+      </c>
+      <c r="N177" s="4" t="n">
+        <v>34.67</v>
+      </c>
+      <c r="O177" s="4" t="n">
+        <v>171.1</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="1" t="inlineStr">
+        <is>
+          <t>001800</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>오리온홀딩스</t>
+        </is>
+      </c>
+      <c r="C178" s="3" t="n">
+        <v>23650</v>
+      </c>
+      <c r="D178" s="3" t="n">
+        <v>30033.77</v>
+      </c>
+      <c r="E178" s="2" t="n">
+        <v>-21.26</v>
+      </c>
+      <c r="F178" s="2" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="G178" s="2" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="H178" s="2" t="n">
+        <v>6.33</v>
+      </c>
+      <c r="I178" s="2" t="n">
+        <v>12.65</v>
+      </c>
+      <c r="J178" s="2" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K178" s="2" t="n">
+        <v>9.16</v>
+      </c>
+      <c r="L178" s="2" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="M178" s="2" t="inlineStr">
+        <is>
+          <t>저평가</t>
+        </is>
+      </c>
+      <c r="N178" s="4" t="n">
+        <v>-3.65</v>
+      </c>
+      <c r="O178" s="2" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="1" t="inlineStr">
+        <is>
+          <t>007310</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>오뚜기</t>
+        </is>
+      </c>
+      <c r="C179" s="3" t="n">
+        <v>367000</v>
+      </c>
+      <c r="D179" s="3" t="n">
+        <v>532494.59</v>
+      </c>
+      <c r="E179" s="2" t="n">
+        <v>-31.08</v>
+      </c>
+      <c r="F179" s="2" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="G179" s="2" t="n">
+        <v>10.91</v>
+      </c>
+      <c r="H179" s="2" t="n">
+        <v>6.27</v>
+      </c>
+      <c r="I179" s="2" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="J179" s="2" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="K179" s="2" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="L179" s="2" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="M179" s="2" t="inlineStr">
+        <is>
+          <t>저평가</t>
+        </is>
+      </c>
+      <c r="N179" s="4" t="n">
+        <v>-20.14</v>
+      </c>
+      <c r="O179" s="2" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="1" t="inlineStr">
+        <is>
+          <t>034230</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>파라다이스</t>
+        </is>
+      </c>
+      <c r="C180" s="3" t="n">
+        <v>15170</v>
+      </c>
+      <c r="D180" s="3" t="n">
+        <v>547746.86</v>
+      </c>
+      <c r="E180" s="2" t="n">
+        <v>-97.23</v>
+      </c>
+      <c r="F180" s="2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G180" s="2" t="n">
+        <v>14.07</v>
+      </c>
+      <c r="H180" s="2" t="n">
+        <v>5.51</v>
+      </c>
+      <c r="I180" s="2" t="n">
+        <v>28.94</v>
+      </c>
+      <c r="J180" s="2" t="n">
+        <v>6.27</v>
+      </c>
+      <c r="K180" s="2" t="n">
+        <v>21.78</v>
+      </c>
+      <c r="L180" s="2" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="M180" s="2" t="inlineStr">
+        <is>
+          <t>저평가</t>
+        </is>
+      </c>
+      <c r="N180" s="4" t="n">
+        <v>14.47</v>
+      </c>
+      <c r="O180" s="4" t="n">
+        <v>181.74</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="1" t="inlineStr">
+        <is>
+          <t>000210</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>DL</t>
+        </is>
+      </c>
+      <c r="C181" s="3" t="n">
+        <v>65600</v>
+      </c>
+      <c r="D181" s="3" t="n">
+        <v>107775.16</v>
+      </c>
+      <c r="E181" s="2" t="n">
+        <v>-39.13</v>
+      </c>
+      <c r="F181" s="2" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="G181" s="2" t="n">
+        <v>5.12</v>
+      </c>
+      <c r="H181" s="2" t="n">
+        <v>7.27</v>
+      </c>
+      <c r="I181" s="2" t="n">
+        <v>-20.77</v>
+      </c>
+      <c r="J181" s="2" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="K181" s="2" t="n">
+        <v>-24.62</v>
+      </c>
+      <c r="L181" s="2" t="inlineStr"/>
+      <c r="M181" s="2" t="inlineStr">
+        <is>
+          <t>저평가</t>
+        </is>
+      </c>
+      <c r="N181" s="4" t="n">
+        <v>-27.64</v>
+      </c>
+      <c r="O181" s="2" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="5" t="inlineStr">
+        <is>
+          <t>229640</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>LS에코에너지</t>
+        </is>
+      </c>
+      <c r="C182" s="6" t="n">
+        <v>44750</v>
+      </c>
+      <c r="D182" s="6" t="n">
+        <v>18973.84</v>
+      </c>
+      <c r="E182" t="n">
+        <v>135.85</v>
+      </c>
+      <c r="F182" t="n">
+        <v>5.31</v>
+      </c>
+      <c r="G182" t="n">
+        <v>29.89</v>
+      </c>
+      <c r="H182" t="n">
+        <v>19.53</v>
+      </c>
+      <c r="I182" t="n">
+        <v>14.59</v>
+      </c>
+      <c r="J182" t="n">
+        <v>18.07</v>
+      </c>
+      <c r="K182" t="n">
+        <v>-3.74</v>
+      </c>
+      <c r="L182" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>고평가</t>
+        </is>
+      </c>
+      <c r="N182" s="7" t="n">
+        <v>11.76</v>
+      </c>
+      <c r="O182" s="7" t="n">
+        <v>11.76</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="1" t="inlineStr">
+        <is>
+          <t>032350</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>롯데관광개발</t>
+        </is>
+      </c>
+      <c r="C183" s="3" t="n">
+        <v>17160</v>
+      </c>
+      <c r="D183" s="3" t="n">
+        <v>21312.9</v>
+      </c>
+      <c r="E183" s="2" t="n">
+        <v>-19.49</v>
+      </c>
+      <c r="F183" s="2" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="G183" s="2" t="n">
+        <v>16.23</v>
+      </c>
+      <c r="H183" s="2" t="n">
+        <v>20.36</v>
+      </c>
+      <c r="I183" s="2" t="n">
+        <v>62.28</v>
+      </c>
+      <c r="J183" s="2" t="n">
+        <v>28.73</v>
+      </c>
+      <c r="K183" s="2" t="n">
+        <v>28.29</v>
+      </c>
+      <c r="L183" s="2" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="M183" s="2" t="inlineStr">
+        <is>
+          <t>저평가</t>
+        </is>
+      </c>
+      <c r="N183" s="4" t="n">
+        <v>267.44</v>
+      </c>
+      <c r="O183" s="4" t="n">
+        <v>340.92</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="1" t="inlineStr">
+        <is>
+          <t>077970</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>STX엔진</t>
+        </is>
+      </c>
+      <c r="C184" s="3" t="n">
+        <v>33200</v>
+      </c>
+      <c r="D184" s="3" t="n">
+        <v>47779.22</v>
+      </c>
+      <c r="E184" s="2" t="n">
+        <v>-30.51</v>
+      </c>
+      <c r="F184" s="2" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="G184" s="2" t="n">
+        <v>16.23</v>
+      </c>
+      <c r="H184" s="2" t="n">
+        <v>21.55</v>
+      </c>
+      <c r="I184" s="2" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="J184" s="2" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="K184" s="2" t="n">
+        <v>-12.95</v>
+      </c>
+      <c r="L184" s="2" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="M184" s="2" t="inlineStr">
+        <is>
+          <t>저평가</t>
+        </is>
+      </c>
+      <c r="N184" s="4" t="n">
+        <v>64.93000000000001</v>
+      </c>
+      <c r="O184" s="2" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="1" t="inlineStr">
+        <is>
+          <t>004000</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>롯데정밀화학</t>
+        </is>
+      </c>
+      <c r="C185" s="3" t="n">
+        <v>51200</v>
+      </c>
+      <c r="D185" s="3" t="n">
+        <v>75522.08</v>
+      </c>
+      <c r="E185" s="2" t="n">
+        <v>-32.21</v>
+      </c>
+      <c r="F185" s="2" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="G185" s="2" t="n">
+        <v>9.07</v>
+      </c>
+      <c r="H185" s="2" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="I185" s="2" t="n">
+        <v>17.93</v>
+      </c>
+      <c r="J185" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="K185" s="2" t="n">
+        <v>12.78</v>
+      </c>
+      <c r="L185" s="2" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="M185" s="2" t="inlineStr">
+        <is>
+          <t>저평가</t>
+        </is>
+      </c>
+      <c r="N185" s="4" t="n">
+        <v>36.17</v>
+      </c>
+      <c r="O185" s="4" t="n">
+        <v>-17.95</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="1" t="inlineStr">
+        <is>
+          <t>131290</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>티에스이</t>
+        </is>
+      </c>
+      <c r="C186" s="3" t="n">
+        <v>118200</v>
+      </c>
+      <c r="D186" s="3" t="n">
+        <v>537845.9399999999</v>
+      </c>
+      <c r="E186" s="2" t="n">
+        <v>-78.02</v>
+      </c>
+      <c r="F186" s="2" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="G186" s="2" t="n">
+        <v>19.63</v>
+      </c>
+      <c r="H186" s="2" t="n">
+        <v>16.26</v>
+      </c>
+      <c r="I186" s="2" t="n">
+        <v>20.13</v>
+      </c>
+      <c r="J186" s="2" t="n">
+        <v>16.83</v>
+      </c>
+      <c r="K186" s="2" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="L186" s="2" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="M186" s="2" t="inlineStr">
+        <is>
+          <t>저평가</t>
+        </is>
+      </c>
+      <c r="N186" s="4" t="n">
+        <v>23.31</v>
+      </c>
+      <c r="O186" s="2" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="1" t="inlineStr">
+        <is>
+          <t>100840</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>SNT에너지</t>
+        </is>
+      </c>
+      <c r="C187" s="3" t="n">
+        <v>62200</v>
+      </c>
+      <c r="D187" s="3" t="n">
+        <v>112991.84</v>
+      </c>
+      <c r="E187" s="2" t="n">
+        <v>-44.95</v>
+      </c>
+      <c r="F187" s="2" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="G187" s="2" t="n">
+        <v>11.92</v>
+      </c>
+      <c r="H187" s="2" t="n">
+        <v>24.85</v>
+      </c>
+      <c r="I187" s="2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J187" s="2" t="n">
+        <v>19.23</v>
+      </c>
+      <c r="K187" s="2" t="n">
+        <v>-11.79</v>
+      </c>
+      <c r="L187" s="2" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="M187" s="2" t="inlineStr">
+        <is>
+          <t>저평가</t>
+        </is>
+      </c>
+      <c r="N187" s="4" t="n">
+        <v>105.43</v>
+      </c>
+      <c r="O187" s="2" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="1" t="inlineStr">
+        <is>
+          <t>300720</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>한일시멘트</t>
+        </is>
+      </c>
+      <c r="C188" s="3" t="n">
+        <v>17260</v>
+      </c>
+      <c r="D188" s="3" t="n">
+        <v>45139.53</v>
+      </c>
+      <c r="E188" s="2" t="n">
+        <v>-61.76</v>
+      </c>
+      <c r="F188" s="2" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G188" s="2" t="n">
+        <v>21.52</v>
+      </c>
+      <c r="H188" s="2" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="I188" s="2" t="n">
+        <v>45.11</v>
+      </c>
+      <c r="J188" s="2" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K188" s="2" t="n">
+        <v>45.4</v>
+      </c>
+      <c r="L188" s="2" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="M188" s="2" t="inlineStr">
+        <is>
+          <t>저평가</t>
+        </is>
+      </c>
+      <c r="N188" s="4" t="n">
+        <v>-51.11</v>
+      </c>
+      <c r="O188" s="4" t="n">
+        <v>680.59</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="1" t="inlineStr">
+        <is>
+          <t>181710</t>
+        </is>
+      </c>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>NHN</t>
+        </is>
+      </c>
+      <c r="C189" s="3" t="n">
+        <v>38200</v>
+      </c>
+      <c r="D189" s="3" t="n">
+        <v>61843.83</v>
+      </c>
+      <c r="E189" s="2" t="n">
+        <v>-38.23</v>
+      </c>
+      <c r="F189" s="2" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="G189" s="2" t="n">
+        <v>11.42</v>
+      </c>
+      <c r="H189" s="2" t="n">
+        <v>7.11</v>
+      </c>
+      <c r="I189" s="2" t="n">
+        <v>31.61</v>
+      </c>
+      <c r="J189" s="2" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="K189" s="2" t="n">
+        <v>22.36</v>
+      </c>
+      <c r="L189" s="2" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="M189" s="2" t="inlineStr">
+        <is>
+          <t>저평가</t>
+        </is>
+      </c>
+      <c r="N189" s="2" t="inlineStr"/>
+      <c r="O189" s="4" t="n">
+        <v>395.88</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="1" t="inlineStr">
+        <is>
+          <t>096530</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>씨젠</t>
+        </is>
+      </c>
+      <c r="C190" s="3" t="n">
+        <v>23900</v>
+      </c>
+      <c r="D190" s="3" t="n">
+        <v>29239.37</v>
+      </c>
+      <c r="E190" s="2" t="n">
+        <v>-18.26</v>
+      </c>
+      <c r="F190" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G190" s="2" t="n">
+        <v>20.92</v>
+      </c>
+      <c r="H190" s="2" t="n">
+        <v>5.73</v>
+      </c>
+      <c r="I190" s="2" t="n">
+        <v>45.07</v>
+      </c>
+      <c r="J190" s="2" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="K190" s="2" t="n">
+        <v>42.41</v>
+      </c>
+      <c r="L190" s="2" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="M190" s="2" t="inlineStr">
+        <is>
+          <t>저평가</t>
+        </is>
+      </c>
+      <c r="N190" s="2" t="inlineStr"/>
+      <c r="O190" s="4" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="5" t="inlineStr">
+        <is>
+          <t>189300</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>인텔리안테크</t>
+        </is>
+      </c>
+      <c r="C191" s="6" t="n">
+        <v>114500</v>
+      </c>
+      <c r="D191" s="6" t="n">
+        <v>75710.31</v>
+      </c>
+      <c r="E191" t="n">
+        <v>51.23</v>
+      </c>
+      <c r="F191" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="G191" t="n">
+        <v>38.07</v>
+      </c>
+      <c r="H191" t="n">
+        <v>11.33</v>
+      </c>
+      <c r="I191" t="n">
+        <v>44.85</v>
+      </c>
+      <c r="J191" t="n">
+        <v>12.81</v>
+      </c>
+      <c r="K191" t="n">
+        <v>27.18</v>
+      </c>
+      <c r="L191" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>고평가</t>
+        </is>
+      </c>
+      <c r="N191" t="inlineStr"/>
+      <c r="O191" s="7" t="n">
+        <v>990.91</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="1" t="inlineStr">
+        <is>
+          <t>000080</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>하이트진로</t>
+        </is>
+      </c>
+      <c r="C192" s="3" t="n">
+        <v>17400</v>
+      </c>
+      <c r="D192" s="3" t="n">
+        <v>27927.1</v>
+      </c>
+      <c r="E192" s="2" t="n">
+        <v>-37.69</v>
+      </c>
+      <c r="F192" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="G192" s="2" t="n">
+        <v>10.81</v>
+      </c>
+      <c r="H192" s="2" t="n">
+        <v>9.59</v>
+      </c>
+      <c r="I192" s="2" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="J192" s="2" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="K192" s="2" t="n">
+        <v>-1.46</v>
+      </c>
+      <c r="L192" s="2" t="inlineStr"/>
+      <c r="M192" s="2" t="inlineStr">
+        <is>
+          <t>저평가</t>
+        </is>
+      </c>
+      <c r="N192" s="4" t="n">
+        <v>-17.2</v>
+      </c>
+      <c r="O192" s="4" t="n">
+        <v>204.96</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="5" t="inlineStr">
+        <is>
+          <t>388210</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>씨엠티엑스</t>
+        </is>
+      </c>
+      <c r="C193" s="6" t="n">
+        <v>127500</v>
+      </c>
+      <c r="D193" s="6" t="n">
+        <v>134311.28</v>
+      </c>
+      <c r="E193" t="n">
+        <v>-5.07</v>
+      </c>
+      <c r="F193" t="n">
+        <v>6.84</v>
+      </c>
+      <c r="G193" t="n">
+        <v>17.76</v>
+      </c>
+      <c r="H193" t="n">
+        <v>38.01</v>
+      </c>
+      <c r="I193" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="J193" t="n">
+        <v>46.04</v>
+      </c>
+      <c r="K193" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="L193" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>적정</t>
+        </is>
+      </c>
+      <c r="N193" s="7" t="n">
+        <v>119.49</v>
+      </c>
+      <c r="O193" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="5" t="inlineStr">
+        <is>
+          <t>023160</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>태광</t>
+        </is>
+      </c>
+      <c r="C194" s="6" t="n">
+        <v>46650</v>
+      </c>
+      <c r="D194" s="6" t="n">
+        <v>48321.45</v>
+      </c>
+      <c r="E194" t="n">
+        <v>-3.46</v>
+      </c>
+      <c r="F194" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="G194" t="n">
+        <v>19.86</v>
+      </c>
+      <c r="H194" t="n">
+        <v>8.67</v>
+      </c>
+      <c r="I194" t="n">
+        <v>18.94</v>
+      </c>
+      <c r="J194" t="n">
+        <v>7.19</v>
+      </c>
+      <c r="K194" t="n">
+        <v>10.84</v>
+      </c>
+      <c r="L194" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>적정</t>
+        </is>
+      </c>
+      <c r="N194" s="7" t="n">
+        <v>-3.01</v>
+      </c>
+      <c r="O194" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="5" t="inlineStr">
+        <is>
+          <t>124500</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>아이티센글로벌</t>
+        </is>
+      </c>
+      <c r="C195" s="6" t="n">
+        <v>52000</v>
+      </c>
+      <c r="D195" s="6" t="n">
+        <v>54388.6</v>
+      </c>
+      <c r="E195" t="n">
+        <v>-4.39</v>
+      </c>
+      <c r="F195" t="n">
+        <v>8.49</v>
+      </c>
+      <c r="G195" t="n">
+        <v>32.98</v>
+      </c>
+      <c r="H195" t="n">
+        <v>26.78</v>
+      </c>
+      <c r="I195" t="n">
+        <v>8.619999999999999</v>
+      </c>
+      <c r="J195" t="n">
+        <v>27.95</v>
+      </c>
+      <c r="K195" t="n">
+        <v>-8.44</v>
+      </c>
+      <c r="L195" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>적정</t>
+        </is>
+      </c>
+      <c r="N195" s="7" t="n">
+        <v>377.65</v>
+      </c>
+      <c r="O195" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="5" t="inlineStr">
+        <is>
+          <t>001740</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>SK네트웍스</t>
+        </is>
+      </c>
+      <c r="C196" s="6" t="n">
+        <v>5360</v>
+      </c>
+      <c r="D196" s="6" t="n">
+        <v>3790.43</v>
+      </c>
+      <c r="E196" t="n">
+        <v>41.41</v>
+      </c>
+      <c r="F196" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="G196" t="n">
+        <v>18.96</v>
+      </c>
+      <c r="H196" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="I196" t="n">
+        <v>14.86</v>
+      </c>
+      <c r="J196" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="K196" t="n">
+        <v>14.24</v>
+      </c>
+      <c r="L196" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>고평가</t>
+        </is>
+      </c>
+      <c r="N196" s="7" t="n">
+        <v>46.06</v>
+      </c>
+      <c r="O196" s="7" t="n">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="1" t="inlineStr">
+        <is>
+          <t>089860</t>
+        </is>
+      </c>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>롯데렌탈</t>
+        </is>
+      </c>
+      <c r="C197" s="3" t="n">
+        <v>32400</v>
+      </c>
+      <c r="D197" s="3" t="n">
+        <v>53158</v>
+      </c>
+      <c r="E197" s="2" t="n">
+        <v>-39.05</v>
+      </c>
+      <c r="F197" s="2" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G197" s="2" t="n">
+        <v>7.36</v>
+      </c>
+      <c r="H197" s="2" t="n">
+        <v>9.630000000000001</v>
+      </c>
+      <c r="I197" s="2" t="n">
+        <v>11.04</v>
+      </c>
+      <c r="J197" s="2" t="n">
+        <v>6.98</v>
+      </c>
+      <c r="K197" s="2" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="L197" s="2" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="M197" s="2" t="inlineStr">
+        <is>
+          <t>저평가</t>
+        </is>
+      </c>
+      <c r="N197" s="4" t="n">
+        <v>14.78</v>
+      </c>
+      <c r="O197" s="4" t="n">
+        <v>-3.63</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="5" t="inlineStr">
+        <is>
+          <t>036540</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>SFA반도체</t>
+        </is>
+      </c>
+      <c r="C198" s="6" t="n">
+        <v>6900</v>
+      </c>
+      <c r="D198" s="6" t="n">
+        <v>3062.07</v>
+      </c>
+      <c r="E198" t="n">
+        <v>125.34</v>
+      </c>
+      <c r="F198" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="G198" t="n">
+        <v>35.75</v>
+      </c>
+      <c r="H198" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="I198" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="J198" t="n">
+        <v>9.529999999999999</v>
+      </c>
+      <c r="K198" t="n">
+        <v>42.2</v>
+      </c>
+      <c r="L198" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>고평가</t>
+        </is>
+      </c>
+      <c r="N198" t="inlineStr"/>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t>적자전환</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="1" t="inlineStr">
+        <is>
+          <t>089970</t>
+        </is>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>브이엠</t>
+        </is>
+      </c>
+      <c r="C199" s="3" t="n">
+        <v>46000</v>
+      </c>
+      <c r="D199" s="3" t="n">
+        <v>74099.63</v>
+      </c>
+      <c r="E199" s="2" t="n">
+        <v>-37.92</v>
+      </c>
+      <c r="F199" s="2" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="G199" s="2" t="n">
+        <v>18.78</v>
+      </c>
+      <c r="H199" s="2" t="n">
+        <v>30.57</v>
+      </c>
+      <c r="I199" s="2" t="n">
+        <v>26.57</v>
+      </c>
+      <c r="J199" s="2" t="n">
+        <v>27.91</v>
+      </c>
+      <c r="K199" s="2" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="L199" s="2" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="M199" s="2" t="inlineStr">
+        <is>
+          <t>저평가</t>
+        </is>
+      </c>
+      <c r="N199" s="2" t="inlineStr"/>
+      <c r="O199" s="4" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="1" t="inlineStr">
+        <is>
+          <t>032500</t>
+        </is>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>케이엠더블유</t>
+        </is>
+      </c>
+      <c r="C200" s="3" t="n">
+        <v>26900</v>
+      </c>
+      <c r="D200" s="3" t="n">
+        <v>35696.2</v>
+      </c>
+      <c r="E200" s="2" t="n">
+        <v>-24.64</v>
+      </c>
+      <c r="F200" s="2" t="n">
+        <v>7.36</v>
+      </c>
+      <c r="G200" s="2" t="n">
+        <v>82.81999999999999</v>
+      </c>
+      <c r="H200" s="2" t="n">
+        <v>9.15</v>
+      </c>
+      <c r="I200" s="2" t="n">
+        <v>824.41</v>
+      </c>
+      <c r="J200" s="2" t="n">
+        <v>82.20999999999999</v>
+      </c>
+      <c r="K200" s="2" t="n">
+        <v>536.83</v>
+      </c>
+      <c r="L200" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M200" s="2" t="inlineStr">
+        <is>
+          <t>저평가</t>
+        </is>
+      </c>
+      <c r="N200" s="2" t="inlineStr"/>
+      <c r="O200" s="2" t="inlineStr">
+        <is>
+          <t>적자전환</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="1" t="inlineStr">
+        <is>
+          <t>005300</t>
+        </is>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>롯데칠성</t>
+        </is>
+      </c>
+      <c r="C201" s="3" t="n">
+        <v>118200</v>
+      </c>
+      <c r="D201" s="3" t="n">
+        <v>211447.51</v>
+      </c>
+      <c r="E201" s="2" t="n">
+        <v>-44.1</v>
+      </c>
+      <c r="F201" s="2" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G201" s="2" t="n">
+        <v>10.24</v>
+      </c>
+      <c r="H201" s="2" t="n">
+        <v>7.17</v>
+      </c>
+      <c r="I201" s="2" t="n">
+        <v>18.04</v>
+      </c>
+      <c r="J201" s="2" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="K201" s="2" t="n">
+        <v>12.27</v>
+      </c>
+      <c r="L201" s="2" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="M201" s="2" t="inlineStr">
+        <is>
+          <t>저평가</t>
+        </is>
+      </c>
+      <c r="N201" s="4" t="n">
+        <v>44</v>
+      </c>
+      <c r="O201" s="4" t="n">
+        <v>-5.76</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="5" t="inlineStr">
+        <is>
+          <t>420770</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>기가비스</t>
+        </is>
+      </c>
+      <c r="C202" s="6" t="n">
+        <v>85500</v>
+      </c>
+      <c r="D202" s="6" t="n">
+        <v>86364.05</v>
+      </c>
+      <c r="E202" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F202" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="G202" t="n">
+        <v>45.01</v>
+      </c>
+      <c r="H202" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="I202" t="n">
+        <v>85.11</v>
+      </c>
+      <c r="J202" t="n">
+        <v>13.67</v>
+      </c>
+      <c r="K202" t="n">
+        <v>68.83</v>
+      </c>
+      <c r="L202" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>적정</t>
+        </is>
+      </c>
+      <c r="N202" t="inlineStr"/>
+      <c r="O202" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="1" t="inlineStr">
+        <is>
+          <t>280360</t>
+        </is>
+      </c>
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>롯데웰푸드</t>
+        </is>
+      </c>
+      <c r="C203" s="3" t="n">
+        <v>115900</v>
+      </c>
+      <c r="D203" s="3" t="n">
+        <v>227961.99</v>
+      </c>
+      <c r="E203" s="2" t="n">
+        <v>-49.16</v>
+      </c>
+      <c r="F203" s="2" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="G203" s="2" t="n">
+        <v>9.470000000000001</v>
+      </c>
+      <c r="H203" s="2" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="I203" s="2" t="n">
+        <v>19.11</v>
+      </c>
+      <c r="J203" s="2" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="K203" s="2" t="n">
+        <v>15.24</v>
+      </c>
+      <c r="L203" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M203" s="2" t="inlineStr">
+        <is>
+          <t>저평가</t>
+        </is>
+      </c>
+      <c r="N203" s="4" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="O203" s="4" t="n">
+        <v>-14.8</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="5" t="inlineStr">
+        <is>
+          <t>014620</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>성광벤드</t>
+        </is>
+      </c>
+      <c r="C204" s="6" t="n">
+        <v>39800</v>
+      </c>
+      <c r="D204" s="6" t="n">
+        <v>38175.59</v>
+      </c>
+      <c r="E204" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="F204" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="G204" t="n">
+        <v>23.44</v>
+      </c>
+      <c r="H204" t="n">
+        <v>7.77</v>
+      </c>
+      <c r="I204" t="n">
+        <v>21.05</v>
+      </c>
+      <c r="J204" t="n">
+        <v>6.89</v>
+      </c>
+      <c r="K204" t="n">
+        <v>13.77</v>
+      </c>
+      <c r="L204" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>적정</t>
+        </is>
+      </c>
+      <c r="N204" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O204" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="5" t="inlineStr">
+        <is>
+          <t>050890</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>쏠리드</t>
+        </is>
+      </c>
+      <c r="C205" s="6" t="n">
+        <v>17080</v>
+      </c>
+      <c r="D205" s="6" t="n">
+        <v>8100.35</v>
+      </c>
+      <c r="E205" t="n">
+        <v>110.86</v>
+      </c>
+      <c r="F205" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="G205" t="n">
+        <v>25.52</v>
+      </c>
+      <c r="H205" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="I205" t="n">
+        <v>20.65</v>
+      </c>
+      <c r="J205" t="n">
+        <v>9.19</v>
+      </c>
+      <c r="K205" t="n">
+        <v>10.83</v>
+      </c>
+      <c r="L205" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>고평가</t>
+        </is>
+      </c>
+      <c r="N205" s="7" t="n">
+        <v>-5.13</v>
+      </c>
+      <c r="O205" s="7" t="n">
+        <v>656.8200000000001</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="1" t="inlineStr">
+        <is>
+          <t>192080</t>
+        </is>
+      </c>
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>더블유게임즈</t>
+        </is>
+      </c>
+      <c r="C206" s="3" t="n">
+        <v>48550</v>
+      </c>
+      <c r="D206" s="3" t="n">
+        <v>100043.24</v>
+      </c>
+      <c r="E206" s="2" t="n">
+        <v>-51.47</v>
+      </c>
+      <c r="F206" s="2" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="G206" s="2" t="n">
+        <v>5.81</v>
+      </c>
+      <c r="H206" s="2" t="n">
+        <v>13.39</v>
+      </c>
+      <c r="I206" s="2" t="n">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="J206" s="2" t="n">
+        <v>13.38</v>
+      </c>
+      <c r="K206" s="2" t="n">
+        <v>-6.35</v>
+      </c>
+      <c r="L206" s="2" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="M206" s="2" t="inlineStr">
+        <is>
+          <t>저평가</t>
+        </is>
+      </c>
+      <c r="N206" s="4" t="n">
+        <v>-6.67</v>
+      </c>
+      <c r="O206" s="4" t="n">
+        <v>264.36</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="1" t="inlineStr">
+        <is>
+          <t>006650</t>
+        </is>
+      </c>
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>대한유화</t>
+        </is>
+      </c>
+      <c r="C207" s="3" t="n">
+        <v>157500</v>
+      </c>
+      <c r="D207" s="3" t="n">
+        <v>217563.14</v>
+      </c>
+      <c r="E207" s="2" t="n">
+        <v>-27.61</v>
+      </c>
+      <c r="F207" s="2" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="G207" s="2" t="n">
+        <v>13.67</v>
+      </c>
+      <c r="H207" s="2" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="I207" s="2" t="n">
+        <v>76.69</v>
+      </c>
+      <c r="J207" s="2" t="n">
+        <v>6.09</v>
+      </c>
+      <c r="K207" s="2" t="n">
+        <v>68.75</v>
+      </c>
+      <c r="L207" s="2" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="M207" s="2" t="inlineStr">
+        <is>
+          <t>저평가</t>
+        </is>
+      </c>
+      <c r="N207" s="2" t="inlineStr"/>
+      <c r="O207" s="4" t="n">
+        <v>31.02</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="1" t="inlineStr">
+        <is>
+          <t>036530</t>
+        </is>
+      </c>
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>SNT홀딩스</t>
+        </is>
+      </c>
+      <c r="C208" s="3" t="n">
+        <v>62500</v>
+      </c>
+      <c r="D208" s="3" t="n">
+        <v>126887.24</v>
+      </c>
+      <c r="E208" s="2" t="n">
+        <v>-50.74</v>
+      </c>
+      <c r="F208" s="2" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="G208" s="2" t="n">
+        <v>5.34</v>
+      </c>
+      <c r="H208" s="2" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="I208" s="2" t="n">
+        <v>9.890000000000001</v>
+      </c>
+      <c r="J208" s="2" t="n">
+        <v>9.74</v>
+      </c>
+      <c r="K208" s="2" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="L208" s="2" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="M208" s="2" t="inlineStr">
+        <is>
+          <t>저평가</t>
+        </is>
+      </c>
+      <c r="N208" s="2" t="inlineStr"/>
+      <c r="O208" s="2" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="5" t="inlineStr">
+        <is>
+          <t>075580</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>세진중공업</t>
+        </is>
+      </c>
+      <c r="C209" s="6" t="n">
+        <v>17830</v>
+      </c>
+      <c r="D209" s="6" t="n">
+        <v>12293.72</v>
+      </c>
+      <c r="E209" t="n">
+        <v>45.03</v>
+      </c>
+      <c r="F209" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="G209" t="n">
+        <v>19.23</v>
+      </c>
+      <c r="H209" t="n">
+        <v>21.48</v>
+      </c>
+      <c r="I209" t="n">
+        <v>15.53</v>
+      </c>
+      <c r="J209" t="n">
+        <v>18.63</v>
+      </c>
+      <c r="K209" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="L209" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>고평가</t>
+        </is>
+      </c>
+      <c r="N209" s="7" t="n">
+        <v>103.89</v>
+      </c>
+      <c r="O209" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="1" t="inlineStr">
+        <is>
+          <t>005880</t>
+        </is>
+      </c>
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>대한해운</t>
+        </is>
+      </c>
+      <c r="C210" s="3" t="n">
+        <v>3090</v>
+      </c>
+      <c r="D210" s="3" t="n">
+        <v>4763.43</v>
+      </c>
+      <c r="E210" s="2" t="n">
+        <v>-35.13</v>
+      </c>
+      <c r="F210" s="2" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="G210" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H210" s="2" t="n">
+        <v>6.88</v>
+      </c>
+      <c r="I210" s="2" t="n">
+        <v>-1.89</v>
+      </c>
+      <c r="J210" s="2" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="K210" s="2" t="n">
+        <v>-7.85</v>
+      </c>
+      <c r="L210" s="2" t="inlineStr"/>
+      <c r="M210" s="2" t="inlineStr">
+        <is>
+          <t>저평가</t>
+        </is>
+      </c>
+      <c r="N210" s="4" t="n">
+        <v>-36.94</v>
+      </c>
+      <c r="O210" s="4" t="n">
+        <v>273.33</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="5" t="inlineStr">
+        <is>
+          <t>079900</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>전진건설로봇</t>
+        </is>
+      </c>
+      <c r="C211" s="6" t="n">
+        <v>67800</v>
+      </c>
+      <c r="D211" s="6" t="n">
+        <v>64967.94</v>
+      </c>
+      <c r="E211" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="F211" t="n">
+        <v>6.42</v>
+      </c>
+      <c r="G211" t="n">
+        <v>29.62</v>
+      </c>
+      <c r="H211" t="n">
+        <v>21.64</v>
+      </c>
+      <c r="I211" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="J211" t="n">
+        <v>12.87</v>
+      </c>
+      <c r="K211" t="n">
+        <v>13.17</v>
+      </c>
+      <c r="L211" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>적정</t>
+        </is>
+      </c>
+      <c r="N211" s="7" t="n">
+        <v>-8.31</v>
+      </c>
+      <c r="O211" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="1" t="inlineStr">
+        <is>
+          <t>285130</t>
+        </is>
+      </c>
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <t>SK케미칼</t>
+        </is>
+      </c>
+      <c r="C212" s="3" t="n">
+        <v>57000</v>
+      </c>
+      <c r="D212" s="3" t="n">
+        <v>78342.75</v>
+      </c>
+      <c r="E212" s="2" t="n">
+        <v>-27.24</v>
+      </c>
+      <c r="F212" s="2" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="G212" s="2" t="n">
+        <v>14.88</v>
+      </c>
+      <c r="H212" s="2" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="I212" s="2" t="n">
+        <v>104.77</v>
+      </c>
+      <c r="J212" s="2" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="K212" s="2" t="n">
+        <v>98.75</v>
+      </c>
+      <c r="L212" s="2" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="M212" s="2" t="inlineStr">
+        <is>
+          <t>저평가</t>
+        </is>
+      </c>
+      <c r="N212" s="4" t="n">
+        <v>-82.72</v>
+      </c>
+      <c r="O212" s="4" t="n">
+        <v>-83.97</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="5" t="inlineStr">
+        <is>
+          <t>122870</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>와이지엔터테인먼트</t>
+        </is>
+      </c>
+      <c r="C213" s="6" t="n">
+        <v>51200</v>
+      </c>
+      <c r="D213" s="6" t="n">
+        <v>39586</v>
+      </c>
+      <c r="E213" t="n">
+        <v>29.34</v>
+      </c>
+      <c r="F213" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="G213" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="H213" t="n">
+        <v>12.09</v>
+      </c>
+      <c r="I213" t="n">
+        <v>-4.12</v>
+      </c>
+      <c r="J213" t="n">
+        <v>9.42</v>
+      </c>
+      <c r="K213" t="n">
+        <v>-13.48</v>
+      </c>
+      <c r="L213" t="inlineStr"/>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>고평가</t>
+        </is>
+      </c>
+      <c r="N213" t="inlineStr"/>
+      <c r="O213" s="7" t="n">
+        <v>109.64</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="5" t="inlineStr">
+        <is>
+          <t>298050</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>HS효성첨단소재</t>
+        </is>
+      </c>
+      <c r="C214" s="6" t="n">
+        <v>213500</v>
+      </c>
+      <c r="D214" s="6" t="n">
+        <v>219887.84</v>
+      </c>
+      <c r="E214" t="n">
+        <v>-2.91</v>
+      </c>
+      <c r="F214" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="G214" t="n">
+        <v>15.63</v>
+      </c>
+      <c r="H214" t="n">
+        <v>6.62</v>
+      </c>
+      <c r="I214" t="n">
+        <v>54.29</v>
+      </c>
+      <c r="J214" t="n">
+        <v>8.18</v>
+      </c>
+      <c r="K214" t="n">
+        <v>31.12</v>
+      </c>
+      <c r="L214" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>적정</t>
+        </is>
+      </c>
+      <c r="N214" s="7" t="n">
+        <v>-28.51</v>
+      </c>
+      <c r="O214" s="7" t="n">
+        <v>-28.51</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="1" t="inlineStr">
+        <is>
+          <t>204270</t>
+        </is>
+      </c>
+      <c r="B215" s="2" t="inlineStr">
+        <is>
+          <t>제이앤티씨</t>
+        </is>
+      </c>
+      <c r="C215" s="3" t="n">
+        <v>16310</v>
+      </c>
+      <c r="D215" s="3" t="n">
+        <v>32768.26</v>
+      </c>
+      <c r="E215" s="2" t="n">
+        <v>-50.23</v>
+      </c>
+      <c r="F215" s="2" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="G215" s="2" t="n">
+        <v>14.07</v>
+      </c>
+      <c r="H215" s="2" t="n">
+        <v>25.26</v>
+      </c>
+      <c r="I215" s="2" t="n">
+        <v>134.46</v>
+      </c>
+      <c r="J215" s="2" t="n">
+        <v>55.41</v>
+      </c>
+      <c r="K215" s="2" t="n">
+        <v>76.20999999999999</v>
+      </c>
+      <c r="L215" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M215" s="2" t="inlineStr">
+        <is>
+          <t>저평가</t>
+        </is>
+      </c>
+      <c r="N215" s="2" t="inlineStr"/>
+      <c r="O215" s="2" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="1" t="inlineStr">
+        <is>
+          <t>009450</t>
+        </is>
+      </c>
+      <c r="B216" s="2" t="inlineStr">
+        <is>
+          <t>경동나비엔</t>
+        </is>
+      </c>
+      <c r="C216" s="3" t="n">
+        <v>64300</v>
+      </c>
+      <c r="D216" s="3" t="n">
+        <v>125922</v>
+      </c>
+      <c r="E216" s="2" t="n">
+        <v>-48.94</v>
+      </c>
+      <c r="F216" s="2" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="G216" s="2" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H216" s="2" t="n">
+        <v>15.03</v>
+      </c>
+      <c r="I216" s="2" t="n">
+        <v>14.34</v>
+      </c>
+      <c r="J216" s="2" t="n">
+        <v>14.88</v>
+      </c>
+      <c r="K216" s="2" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="L216" s="2" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="M216" s="2" t="inlineStr">
+        <is>
+          <t>저평가</t>
+        </is>
+      </c>
+      <c r="N216" s="4" t="n">
+        <v>8.140000000000001</v>
+      </c>
+      <c r="O216" s="4" t="n">
+        <v>300.56</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="1" t="inlineStr">
+        <is>
+          <t>195870</t>
+        </is>
+      </c>
+      <c r="B217" s="2" t="inlineStr">
+        <is>
+          <t>해성디에스</t>
+        </is>
+      </c>
+      <c r="C217" s="3" t="n">
+        <v>54900</v>
+      </c>
+      <c r="D217" s="3" t="n">
+        <v>80891.96000000001</v>
+      </c>
+      <c r="E217" s="2" t="n">
+        <v>-32.13</v>
+      </c>
+      <c r="F217" s="2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G217" s="2" t="n">
+        <v>10.71</v>
+      </c>
+      <c r="H217" s="2" t="n">
+        <v>13.96</v>
+      </c>
+      <c r="I217" s="2" t="n">
+        <v>19.52</v>
+      </c>
+      <c r="J217" s="2" t="n">
+        <v>13.96</v>
+      </c>
+      <c r="K217" s="2" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="L217" s="2" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="M217" s="2" t="inlineStr">
+        <is>
+          <t>저평가</t>
+        </is>
+      </c>
+      <c r="N217" s="4" t="n">
+        <v>-18.28</v>
+      </c>
+      <c r="O217" s="4" t="n">
+        <v>117.29</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="5" t="inlineStr">
+        <is>
+          <t>009240</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>한샘</t>
+        </is>
+      </c>
+      <c r="C218" s="6" t="n">
+        <v>39300</v>
+      </c>
+      <c r="D218" s="6" t="n">
+        <v>27058.66</v>
+      </c>
+      <c r="E218" t="n">
+        <v>45.24</v>
+      </c>
+      <c r="F218" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="G218" t="n">
+        <v>40.03</v>
+      </c>
+      <c r="H218" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="I218" t="n">
+        <v>63.36</v>
+      </c>
+      <c r="J218" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="K218" t="n">
+        <v>59.46</v>
+      </c>
+      <c r="L218" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>고평가</t>
+        </is>
+      </c>
+      <c r="N218" s="7" t="n">
+        <v>-40.71</v>
+      </c>
+      <c r="O218" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="1" t="inlineStr">
+        <is>
+          <t>064960</t>
+        </is>
+      </c>
+      <c r="B219" s="2" t="inlineStr">
+        <is>
+          <t>SNT모티브</t>
+        </is>
+      </c>
+      <c r="C219" s="3" t="n">
+        <v>34500</v>
+      </c>
+      <c r="D219" s="3" t="n">
+        <v>51150.52</v>
+      </c>
+      <c r="E219" s="2" t="n">
+        <v>-32.55</v>
+      </c>
+      <c r="F219" s="2" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="G219" s="2" t="n">
+        <v>8.93</v>
+      </c>
+      <c r="H219" s="2" t="n">
+        <v>9.51</v>
+      </c>
+      <c r="I219" s="2" t="n">
+        <v>14.81</v>
+      </c>
+      <c r="J219" s="2" t="n">
+        <v>6.58</v>
+      </c>
+      <c r="K219" s="2" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="L219" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M219" s="2" t="inlineStr">
+        <is>
+          <t>저평가</t>
+        </is>
+      </c>
+      <c r="N219" s="4" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="O219" s="4" t="n">
+        <v>-1.59</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="5" t="inlineStr">
+        <is>
+          <t>006730</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>서부T&amp;D</t>
+        </is>
+      </c>
+      <c r="C220" s="6" t="n">
+        <v>13770</v>
+      </c>
+      <c r="D220" s="6" t="n">
+        <v>8955.02</v>
+      </c>
+      <c r="E220" t="n">
+        <v>53.77</v>
+      </c>
+      <c r="F220" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="G220" t="n">
+        <v>18.51</v>
+      </c>
+      <c r="H220" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I220" t="n">
+        <v>16.45</v>
+      </c>
+      <c r="J220" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="K220" t="n">
+        <v>11.67</v>
+      </c>
+      <c r="L220" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>고평가</t>
+        </is>
+      </c>
+      <c r="N220" s="7" t="n">
+        <v>46.15</v>
+      </c>
+      <c r="O220" s="7" t="n">
+        <v>258.67</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="1" t="inlineStr">
+        <is>
+          <t>071320</t>
+        </is>
+      </c>
+      <c r="B221" s="2" t="inlineStr">
+        <is>
+          <t>지역난방공사</t>
+        </is>
+      </c>
+      <c r="C221" s="3" t="n">
+        <v>77000</v>
+      </c>
+      <c r="D221" s="3" t="n">
+        <v>134532.51</v>
+      </c>
+      <c r="E221" s="2" t="n">
+        <v>-42.76</v>
+      </c>
+      <c r="F221" s="2" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="G221" s="2" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="H221" s="2" t="n">
+        <v>8.02</v>
+      </c>
+      <c r="I221" s="2" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="J221" s="2" t="n">
+        <v>5.53</v>
+      </c>
+      <c r="K221" s="2" t="n">
+        <v>-3.12</v>
+      </c>
+      <c r="L221" s="2" t="inlineStr"/>
+      <c r="M221" s="2" t="inlineStr">
+        <is>
+          <t>저평가</t>
+        </is>
+      </c>
+      <c r="N221" s="4" t="n">
+        <v>-20.91</v>
+      </c>
+      <c r="O221" s="4" t="n">
+        <v>-18.78</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="5" t="inlineStr">
+        <is>
+          <t>003160</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>디아이</t>
+        </is>
+      </c>
+      <c r="C222" s="6" t="n">
+        <v>31450</v>
+      </c>
+      <c r="D222" s="6" t="n">
+        <v>15159.09</v>
+      </c>
+      <c r="E222" t="n">
+        <v>107.47</v>
+      </c>
+      <c r="F222" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="G222" t="n">
+        <v>25.63</v>
+      </c>
+      <c r="H222" t="n">
+        <v>18.54</v>
+      </c>
+      <c r="I222" t="n">
+        <v>16.13</v>
+      </c>
+      <c r="J222" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="K222" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="L222" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>고평가</t>
+        </is>
+      </c>
+      <c r="N222" s="7" t="n">
+        <v>24.24</v>
+      </c>
+      <c r="O222" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" s="5" t="inlineStr">
+        <is>
+          <t>499790</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>GS피앤엘</t>
+        </is>
+      </c>
+      <c r="C223" s="6" t="n">
+        <v>44750</v>
+      </c>
+      <c r="D223" s="6" t="n">
+        <v>40733.09</v>
+      </c>
+      <c r="E223" t="n">
+        <v>9.859999999999999</v>
+      </c>
+      <c r="F223" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="G223" t="n">
+        <v>16.18</v>
+      </c>
+      <c r="H223" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="I223" t="n">
+        <v>21.68</v>
+      </c>
+      <c r="J223" t="n">
+        <v>7.11</v>
+      </c>
+      <c r="K223" t="n">
+        <v>13.99</v>
+      </c>
+      <c r="L223" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>적정</t>
+        </is>
+      </c>
+      <c r="N223" s="7" t="n">
+        <v>32.24</v>
+      </c>
+      <c r="O223" s="7" t="n">
+        <v>-30.69</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="1" t="inlineStr">
+        <is>
+          <t>030190</t>
+        </is>
+      </c>
+      <c r="B224" s="2" t="inlineStr">
+        <is>
+          <t>NICE평가정보</t>
+        </is>
+      </c>
+      <c r="C224" s="3" t="n">
+        <v>15020</v>
+      </c>
+      <c r="D224" s="3" t="n">
+        <v>18403.78</v>
+      </c>
+      <c r="E224" s="2" t="n">
+        <v>-18.39</v>
+      </c>
+      <c r="F224" s="2" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="G224" s="2" t="n">
+        <v>9.619999999999999</v>
+      </c>
+      <c r="H224" s="2" t="n">
+        <v>18.64</v>
+      </c>
+      <c r="I224" s="2" t="n">
+        <v>9.08</v>
+      </c>
+      <c r="J224" s="2" t="n">
+        <v>12.74</v>
+      </c>
+      <c r="K224" s="2" t="n">
+        <v>-4.13</v>
+      </c>
+      <c r="L224" s="2" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="M224" s="2" t="inlineStr">
+        <is>
+          <t>저평가</t>
+        </is>
+      </c>
+      <c r="N224" s="4" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="O224" s="2" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" s="1" t="inlineStr">
+        <is>
+          <t>248070</t>
+        </is>
+      </c>
+      <c r="B225" s="2" t="inlineStr">
+        <is>
+          <t>솔루엠</t>
+        </is>
+      </c>
+      <c r="C225" s="3" t="n">
+        <v>17990</v>
+      </c>
+      <c r="D225" s="3" t="n">
+        <v>24131.24</v>
+      </c>
+      <c r="E225" s="2" t="n">
+        <v>-25.45</v>
+      </c>
+      <c r="F225" s="2" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="G225" s="2" t="n">
+        <v>15.91</v>
+      </c>
+      <c r="H225" s="2" t="n">
+        <v>10.68</v>
+      </c>
+      <c r="I225" s="2" t="n">
+        <v>36.22</v>
+      </c>
+      <c r="J225" s="2" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="K225" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="L225" s="2" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="M225" s="2" t="inlineStr">
+        <is>
+          <t>저평가</t>
+        </is>
+      </c>
+      <c r="N225" s="4" t="n">
+        <v>-32.71</v>
+      </c>
+      <c r="O225" s="4" t="n">
+        <v>173.53</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="1" t="inlineStr">
+        <is>
+          <t>010780</t>
+        </is>
+      </c>
+      <c r="B226" s="2" t="inlineStr">
+        <is>
+          <t>아이에스동서</t>
+        </is>
+      </c>
+      <c r="C226" s="3" t="n">
+        <v>28450</v>
+      </c>
+      <c r="D226" s="3" t="n">
+        <v>162458.85</v>
+      </c>
+      <c r="E226" s="2" t="n">
+        <v>-82.48999999999999</v>
+      </c>
+      <c r="F226" s="2" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="G226" s="2" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="H226" s="2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I226" s="2" t="n">
+        <v>104.79</v>
+      </c>
+      <c r="J226" s="2" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="K226" s="2" t="n">
+        <v>92.13</v>
+      </c>
+      <c r="L226" s="2" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="M226" s="2" t="inlineStr">
+        <is>
+          <t>저평가</t>
+        </is>
+      </c>
+      <c r="N226" s="4" t="n">
+        <v>-59.87</v>
+      </c>
+      <c r="O226" s="4" t="n">
+        <v>112.81</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="1" t="inlineStr">
+        <is>
+          <t>171090</t>
+        </is>
+      </c>
+      <c r="B227" s="2" t="inlineStr">
+        <is>
+          <t>선익시스템</t>
+        </is>
+      </c>
+      <c r="C227" s="3" t="n">
+        <v>85000</v>
+      </c>
+      <c r="D227" s="3" t="n">
+        <v>272287.8</v>
+      </c>
+      <c r="E227" s="2" t="n">
+        <v>-68.78</v>
+      </c>
+      <c r="F227" s="2" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="G227" s="2" t="n">
+        <v>9.119999999999999</v>
+      </c>
+      <c r="H227" s="2" t="n">
+        <v>47.75</v>
+      </c>
+      <c r="I227" s="2" t="n">
+        <v>19.11</v>
+      </c>
+      <c r="J227" s="2" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="K227" s="2" t="n">
+        <v>-23.2</v>
+      </c>
+      <c r="L227" s="2" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="M227" s="2" t="inlineStr">
+        <is>
+          <t>저평가</t>
+        </is>
+      </c>
+      <c r="N227" s="4" t="n">
+        <v>1311.39</v>
+      </c>
+      <c r="O227" s="2" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" s="1" t="inlineStr">
+        <is>
+          <t>241710</t>
+        </is>
+      </c>
+      <c r="B228" s="2" t="inlineStr">
+        <is>
+          <t>코스메카코리아</t>
+        </is>
+      </c>
+      <c r="C228" s="3" t="n">
+        <v>79300</v>
+      </c>
+      <c r="D228" s="3" t="n">
+        <v>120483.91</v>
+      </c>
+      <c r="E228" s="2" t="n">
+        <v>-34.18</v>
+      </c>
+      <c r="F228" s="2" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="G228" s="2" t="n">
+        <v>12.84</v>
+      </c>
+      <c r="H228" s="2" t="n">
+        <v>22.47</v>
+      </c>
+      <c r="I228" s="2" t="n">
+        <v>15.85</v>
+      </c>
+      <c r="J228" s="2" t="n">
+        <v>23.97</v>
+      </c>
+      <c r="K228" s="2" t="n">
+        <v>-8.140000000000001</v>
+      </c>
+      <c r="L228" s="2" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="M228" s="2" t="inlineStr">
+        <is>
+          <t>저평가</t>
+        </is>
+      </c>
+      <c r="N228" s="4" t="n">
+        <v>38.25</v>
+      </c>
+      <c r="O228" s="4" t="n">
+        <v>313.37</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="5" t="inlineStr">
+        <is>
+          <t>036810</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>에프에스티</t>
+        </is>
+      </c>
+      <c r="C229" s="6" t="n">
+        <v>39450</v>
+      </c>
+      <c r="D229" s="6" t="n">
+        <v>8925.309999999999</v>
+      </c>
+      <c r="E229" t="n">
+        <v>342</v>
+      </c>
+      <c r="F229" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="G229" t="n">
+        <v>95.43000000000001</v>
+      </c>
+      <c r="H229" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="I229" t="n">
+        <v>97.64</v>
+      </c>
+      <c r="J229" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="K229" t="n">
+        <v>80.65000000000001</v>
+      </c>
+      <c r="L229" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>고평가</t>
+        </is>
+      </c>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t>적자전환</t>
+        </is>
+      </c>
+      <c r="O229" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" s="1" t="inlineStr">
+        <is>
+          <t>108320</t>
+        </is>
+      </c>
+      <c r="B230" s="2" t="inlineStr">
+        <is>
+          <t>LX세미콘</t>
+        </is>
+      </c>
+      <c r="C230" s="3" t="n">
+        <v>51300</v>
+      </c>
+      <c r="D230" s="3" t="n">
+        <v>84223.56</v>
+      </c>
+      <c r="E230" s="2" t="n">
+        <v>-39.09</v>
+      </c>
+      <c r="F230" s="2" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="G230" s="2" t="n">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H230" s="2" t="n">
+        <v>8.41</v>
+      </c>
+      <c r="I230" s="2" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="J230" s="2" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="K230" s="2" t="n">
+        <v>7.61</v>
+      </c>
+      <c r="L230" s="2" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="M230" s="2" t="inlineStr">
+        <is>
+          <t>저평가</t>
+        </is>
+      </c>
+      <c r="N230" s="4" t="n">
+        <v>-34.83</v>
+      </c>
+      <c r="O230" s="2" t="inlineStr"/>
+    </row>
+    <row r="231">
+      <c r="A231" s="1" t="inlineStr">
+        <is>
+          <t>456040</t>
+        </is>
+      </c>
+      <c r="B231" s="2" t="inlineStr">
+        <is>
+          <t>OCI</t>
+        </is>
+      </c>
+      <c r="C231" s="3" t="n">
+        <v>93100</v>
+      </c>
+      <c r="D231" s="3" t="n">
+        <v>138494.02</v>
+      </c>
+      <c r="E231" s="2" t="n">
+        <v>-32.78</v>
+      </c>
+      <c r="F231" s="2" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G231" s="2" t="n">
+        <v>9.69</v>
+      </c>
+      <c r="H231" s="2" t="n">
+        <v>7.27</v>
+      </c>
+      <c r="I231" s="2" t="n">
+        <v>21.17</v>
+      </c>
+      <c r="J231" s="2" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="K231" s="2" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="L231" s="2" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="M231" s="2" t="inlineStr">
+        <is>
+          <t>저평가</t>
+        </is>
+      </c>
+      <c r="N231" s="4" t="n">
+        <v>56.86</v>
+      </c>
+      <c r="O231" s="2" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="5" t="inlineStr">
+        <is>
+          <t>005090</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>SGC에너지</t>
+        </is>
+      </c>
+      <c r="C232" s="6" t="n">
+        <v>56900</v>
+      </c>
+      <c r="D232" s="6" t="n">
+        <v>29263.96</v>
+      </c>
+      <c r="E232" t="n">
+        <v>94.44</v>
+      </c>
+      <c r="F232" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="G232" t="n">
+        <v>41.15</v>
+      </c>
+      <c r="H232" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="I232" t="n">
+        <v>177.83</v>
+      </c>
+      <c r="J232" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="K232" t="n">
+        <v>174.13</v>
+      </c>
+      <c r="L232" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>고평가</t>
+        </is>
+      </c>
+      <c r="N232" s="7" t="n">
+        <v>73.86</v>
+      </c>
+      <c r="O232" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="5" t="inlineStr">
+        <is>
+          <t>327260</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>RF머트리얼즈</t>
+        </is>
+      </c>
+      <c r="C233" s="6" t="n">
+        <v>92700</v>
+      </c>
+      <c r="D233" s="6" t="n">
+        <v>23291.51</v>
+      </c>
+      <c r="E233" t="n">
+        <v>298</v>
+      </c>
+      <c r="F233" t="n">
+        <v>9.67</v>
+      </c>
+      <c r="G233" t="n">
+        <v>58.4</v>
+      </c>
+      <c r="H233" t="n">
+        <v>18.44</v>
+      </c>
+      <c r="I233" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="J233" t="n">
+        <v>33.53</v>
+      </c>
+      <c r="K233" t="n">
+        <v>20.82</v>
+      </c>
+      <c r="L233" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>고평가</t>
+        </is>
+      </c>
+      <c r="N233" t="inlineStr"/>
+      <c r="O233" s="7" t="n">
+        <v>393.33</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="1" t="inlineStr">
+        <is>
+          <t>090460</t>
+        </is>
+      </c>
+      <c r="B234" s="2" t="inlineStr">
+        <is>
+          <t>비에이치</t>
+        </is>
+      </c>
+      <c r="C234" s="3" t="n">
+        <v>23350</v>
+      </c>
+      <c r="D234" s="3" t="n">
+        <v>45550.69</v>
+      </c>
+      <c r="E234" s="2" t="n">
+        <v>-48.74</v>
+      </c>
+      <c r="F234" s="2" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G234" s="2" t="n">
+        <v>8.27</v>
+      </c>
+      <c r="H234" s="2" t="n">
+        <v>11.21</v>
+      </c>
+      <c r="I234" s="2" t="n">
+        <v>22.09</v>
+      </c>
+      <c r="J234" s="2" t="n">
+        <v>12.19</v>
+      </c>
+      <c r="K234" s="2" t="n">
+        <v>9.01</v>
+      </c>
+      <c r="L234" s="2" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="M234" s="2" t="inlineStr">
+        <is>
+          <t>저평가</t>
+        </is>
+      </c>
+      <c r="N234" s="4" t="n">
+        <v>-38</v>
+      </c>
+      <c r="O234" s="4" t="n">
+        <v>694.12</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="5" t="inlineStr">
+        <is>
+          <t>011930</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>신성이엔지</t>
+        </is>
+      </c>
+      <c r="C235" s="6" t="n">
+        <v>3785</v>
+      </c>
+      <c r="D235" s="6" t="n">
+        <v>2143.82</v>
+      </c>
+      <c r="E235" t="n">
+        <v>76.55</v>
+      </c>
+      <c r="F235" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G235" t="n">
+        <v>30.83</v>
+      </c>
+      <c r="H235" t="n">
+        <v>8.41</v>
+      </c>
+      <c r="I235" t="n">
+        <v>56.31</v>
+      </c>
+      <c r="J235" t="n">
+        <v>17.01</v>
+      </c>
+      <c r="K235" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="L235" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>고평가</t>
+        </is>
+      </c>
+      <c r="N235" s="7" t="n">
+        <v>-74</v>
+      </c>
+      <c r="O235" s="7" t="n">
+        <v>-83.75</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="1" t="inlineStr">
+        <is>
+          <t>033500</t>
+        </is>
+      </c>
+      <c r="B236" s="2" t="inlineStr">
+        <is>
+          <t>동성화인텍</t>
+        </is>
+      </c>
+      <c r="C236" s="3" t="n">
+        <v>25550</v>
+      </c>
+      <c r="D236" s="3" t="n">
+        <v>51001.86</v>
+      </c>
+      <c r="E236" s="2" t="n">
+        <v>-49.9</v>
+      </c>
+      <c r="F236" s="2" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="G236" s="2" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="H236" s="2" t="n">
+        <v>26.44</v>
+      </c>
+      <c r="I236" s="2" t="n">
+        <v>16.28</v>
+      </c>
+      <c r="J236" s="2" t="n">
+        <v>24.27</v>
+      </c>
+      <c r="K236" s="2" t="n">
+        <v>-6.39</v>
+      </c>
+      <c r="L236" s="2" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="M236" s="2" t="inlineStr">
+        <is>
+          <t>저평가</t>
+        </is>
+      </c>
+      <c r="N236" s="4" t="n">
+        <v>34.44</v>
+      </c>
+      <c r="O236" s="4" t="n">
+        <v>202.5</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="1" t="inlineStr">
+        <is>
+          <t>025540</t>
+        </is>
+      </c>
+      <c r="B237" s="2" t="inlineStr">
+        <is>
+          <t>한국단자</t>
+        </is>
+      </c>
+      <c r="C237" s="3" t="n">
+        <v>75600</v>
+      </c>
+      <c r="D237" s="3" t="n">
+        <v>157685.26</v>
+      </c>
+      <c r="E237" s="2" t="n">
+        <v>-52.06</v>
+      </c>
+      <c r="F237" s="2" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="G237" s="2" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="H237" s="2" t="n">
+        <v>10.34</v>
+      </c>
+      <c r="I237" s="2" t="n">
+        <v>8.65</v>
+      </c>
+      <c r="J237" s="2" t="n">
+        <v>8.24</v>
+      </c>
+      <c r="K237" s="2" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="L237" s="2" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="M237" s="2" t="inlineStr">
+        <is>
+          <t>저평가</t>
+        </is>
+      </c>
+      <c r="N237" s="4" t="n">
+        <v>6.97</v>
+      </c>
+      <c r="O237" s="2" t="inlineStr"/>
+    </row>
+    <row r="238">
+      <c r="A238" s="5" t="inlineStr">
+        <is>
+          <t>033240</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>자화전자</t>
+        </is>
+      </c>
+      <c r="C238" s="6" t="n">
+        <v>35100</v>
+      </c>
+      <c r="D238" s="6" t="n">
+        <v>32590.77</v>
+      </c>
+      <c r="E238" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="F238" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="G238" t="n">
+        <v>15.48</v>
+      </c>
+      <c r="H238" t="n">
+        <v>10.27</v>
+      </c>
+      <c r="I238" t="n">
+        <v>14.02</v>
+      </c>
+      <c r="J238" t="n">
+        <v>10.89</v>
+      </c>
+      <c r="K238" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="L238" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M238" t="inlineStr">
+        <is>
+          <t>적정</t>
+        </is>
+      </c>
+      <c r="N238" s="7" t="n">
+        <v>-6.67</v>
+      </c>
+      <c r="O238" s="7" t="n">
+        <v>452.63</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="1" t="inlineStr">
+        <is>
+          <t>114090</t>
+        </is>
+      </c>
+      <c r="B239" s="2" t="inlineStr">
+        <is>
+          <t>GKL</t>
+        </is>
+      </c>
+      <c r="C239" s="3" t="n">
+        <v>12130</v>
+      </c>
+      <c r="D239" s="3" t="n">
+        <v>403410.21</v>
+      </c>
+      <c r="E239" s="2" t="n">
+        <v>-96.98999999999999</v>
+      </c>
+      <c r="F239" s="2" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="G239" s="2" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="H239" s="2" t="n">
+        <v>11.95</v>
+      </c>
+      <c r="I239" s="2" t="n">
+        <v>13.79</v>
+      </c>
+      <c r="J239" s="2" t="n">
+        <v>7.85</v>
+      </c>
+      <c r="K239" s="2" t="n">
+        <v>5.77</v>
+      </c>
+      <c r="L239" s="2" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="M239" s="2" t="inlineStr">
+        <is>
+          <t>저평가</t>
+        </is>
+      </c>
+      <c r="N239" s="4" t="n">
+        <v>-22.77</v>
+      </c>
+      <c r="O239" s="4" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="5" t="inlineStr">
+        <is>
+          <t>086900</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>메디톡스</t>
+        </is>
+      </c>
+      <c r="C240" s="6" t="n">
+        <v>101900</v>
+      </c>
+      <c r="D240" s="6" t="n">
+        <v>65648.13</v>
+      </c>
+      <c r="E240" t="n">
+        <v>55.22</v>
+      </c>
+      <c r="F240" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="G240" t="n">
+        <v>31.47</v>
+      </c>
+      <c r="H240" t="n">
+        <v>5.44</v>
+      </c>
+      <c r="I240" t="n">
+        <v>29.18</v>
+      </c>
+      <c r="J240" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="K240" t="n">
+        <v>20.77</v>
+      </c>
+      <c r="L240" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>고평가</t>
+        </is>
+      </c>
+      <c r="N240" s="7" t="n">
+        <v>-16.26</v>
+      </c>
+      <c r="O240" s="7" t="n">
+        <v>102.38</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="1" t="inlineStr">
+        <is>
+          <t>376300</t>
+        </is>
+      </c>
+      <c r="B241" s="2" t="inlineStr">
+        <is>
+          <t>디어유</t>
+        </is>
+      </c>
+      <c r="C241" s="3" t="n">
+        <v>31150</v>
+      </c>
+      <c r="D241" s="3" t="n">
+        <v>82176.78999999999</v>
+      </c>
+      <c r="E241" s="2" t="n">
+        <v>-62.09</v>
+      </c>
+      <c r="F241" s="2" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="G241" s="2" t="n">
+        <v>16.71</v>
+      </c>
+      <c r="H241" s="2" t="n">
+        <v>18.94</v>
+      </c>
+      <c r="I241" s="2" t="n">
+        <v>26.71</v>
+      </c>
+      <c r="J241" s="2" t="n">
+        <v>18.31</v>
+      </c>
+      <c r="K241" s="2" t="n">
+        <v>8.18</v>
+      </c>
+      <c r="L241" s="2" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="M241" s="2" t="inlineStr">
+        <is>
+          <t>저평가</t>
+        </is>
+      </c>
+      <c r="N241" s="4" t="n">
+        <v>89.09</v>
+      </c>
+      <c r="O241" s="4" t="n">
+        <v>6.12</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="5" t="inlineStr">
+        <is>
+          <t>356860</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>티엘비</t>
+        </is>
+      </c>
+      <c r="C242" s="6" t="n">
+        <v>74500</v>
+      </c>
+      <c r="D242" s="6" t="n">
+        <v>81965.99000000001</v>
+      </c>
+      <c r="E242" t="n">
+        <v>-9.109999999999999</v>
+      </c>
+      <c r="F242" t="n">
+        <v>4.84</v>
+      </c>
+      <c r="G242" t="n">
+        <v>21.75</v>
+      </c>
+      <c r="H242" t="n">
+        <v>25.22</v>
+      </c>
+      <c r="I242" t="n">
+        <v>38.08</v>
+      </c>
+      <c r="J242" t="n">
+        <v>28.54</v>
+      </c>
+      <c r="K242" t="n">
+        <v>7.73</v>
+      </c>
+      <c r="L242" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="M242" t="inlineStr">
+        <is>
+          <t>적정</t>
+        </is>
+      </c>
+      <c r="N242" s="7" t="n">
+        <v>664.71</v>
+      </c>
+      <c r="O242" s="7" t="n">
+        <v>132.14</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="1" t="inlineStr">
+        <is>
+          <t>002350</t>
+        </is>
+      </c>
+      <c r="B243" s="2" t="inlineStr">
+        <is>
+          <t>넥센타이어</t>
+        </is>
+      </c>
+      <c r="C243" s="3" t="n">
+        <v>7500</v>
+      </c>
+      <c r="D243" s="3" t="n">
+        <v>17785.55</v>
+      </c>
+      <c r="E243" s="2" t="n">
+        <v>-57.83</v>
+      </c>
+      <c r="F243" s="2" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="G243" s="2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H243" s="2" t="n">
+        <v>7.65</v>
+      </c>
+      <c r="I243" s="2" t="n">
+        <v>12.03</v>
+      </c>
+      <c r="J243" s="2" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="K243" s="2" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="L243" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M243" s="2" t="inlineStr">
+        <is>
+          <t>저평가</t>
+        </is>
+      </c>
+      <c r="N243" s="4" t="n">
+        <v>-1.05</v>
+      </c>
+      <c r="O243" s="4" t="n">
+        <v>198.77</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="1" t="inlineStr">
+        <is>
+          <t>214320</t>
+        </is>
+      </c>
+      <c r="B244" s="2" t="inlineStr">
+        <is>
+          <t>이노션</t>
+        </is>
+      </c>
+      <c r="C244" s="3" t="n">
+        <v>18220</v>
+      </c>
+      <c r="D244" s="3" t="n">
+        <v>27971.34</v>
+      </c>
+      <c r="E244" s="2" t="n">
+        <v>-34.86</v>
+      </c>
+      <c r="F244" s="2" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="G244" s="2" t="n">
+        <v>7.05</v>
+      </c>
+      <c r="H244" s="2" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="I244" s="2" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="J244" s="2" t="n">
+        <v>5.54</v>
+      </c>
+      <c r="K244" s="2" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="L244" s="2" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="M244" s="2" t="inlineStr">
+        <is>
+          <t>저평가</t>
+        </is>
+      </c>
+      <c r="N244" s="4" t="n">
+        <v>12.42</v>
+      </c>
+      <c r="O244" s="4" t="n">
+        <v>-10.9</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="5" t="inlineStr">
+        <is>
+          <t>126340</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>비나텍</t>
+        </is>
+      </c>
+      <c r="C245" s="6" t="n">
+        <v>104700</v>
+      </c>
+      <c r="D245" s="6" t="n">
+        <v>36096.45</v>
+      </c>
+      <c r="E245" t="n">
+        <v>190.06</v>
+      </c>
+      <c r="F245" t="n">
+        <v>7.13</v>
+      </c>
+      <c r="G245" t="n">
+        <v>51.97</v>
+      </c>
+      <c r="H245" t="n">
+        <v>15.47</v>
+      </c>
+      <c r="I245" t="n">
+        <v>70.56999999999999</v>
+      </c>
+      <c r="J245" t="n">
+        <v>18.69</v>
+      </c>
+      <c r="K245" t="n">
+        <v>45.38</v>
+      </c>
+      <c r="L245" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>고평가</t>
+        </is>
+      </c>
+      <c r="N245" t="inlineStr"/>
+      <c r="O245" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" s="1" t="inlineStr">
+        <is>
+          <t>093050</t>
+        </is>
+      </c>
+      <c r="B246" s="2" t="inlineStr">
+        <is>
+          <t>LF</t>
+        </is>
+      </c>
+      <c r="C246" s="3" t="n">
+        <v>24850</v>
+      </c>
+      <c r="D246" s="3" t="n">
+        <v>50615.65</v>
+      </c>
+      <c r="E246" s="2" t="n">
+        <v>-50.9</v>
+      </c>
+      <c r="F246" s="2" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="G246" s="2" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="H246" s="2" t="n">
+        <v>8.460000000000001</v>
+      </c>
+      <c r="I246" s="2" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="J246" s="2" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="K246" s="2" t="n">
+        <v>-5.67</v>
+      </c>
+      <c r="L246" s="2" t="inlineStr"/>
+      <c r="M246" s="2" t="inlineStr">
+        <is>
+          <t>저평가</t>
+        </is>
+      </c>
+      <c r="N246" s="4" t="n">
+        <v>33.31</v>
+      </c>
+      <c r="O246" s="2" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" s="1" t="inlineStr">
+        <is>
+          <t>001680</t>
+        </is>
+      </c>
+      <c r="B247" s="2" t="inlineStr">
+        <is>
+          <t>대상</t>
+        </is>
+      </c>
+      <c r="C247" s="3" t="n">
+        <v>20850</v>
+      </c>
+      <c r="D247" s="3" t="n">
+        <v>50515.73</v>
+      </c>
+      <c r="E247" s="2" t="n">
+        <v>-58.73</v>
+      </c>
+      <c r="F247" s="2" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="G247" s="2" t="n">
+        <v>7.21</v>
+      </c>
+      <c r="H247" s="2" t="n">
+        <v>7.49</v>
+      </c>
+      <c r="I247" s="2" t="n">
+        <v>14.91</v>
+      </c>
+      <c r="J247" s="2" t="n">
+        <v>7.88</v>
+      </c>
+      <c r="K247" s="2" t="n">
+        <v>-8.279999999999999</v>
+      </c>
+      <c r="L247" s="2" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="M247" s="2" t="inlineStr">
+        <is>
+          <t>저평가</t>
+        </is>
+      </c>
+      <c r="N247" s="4" t="n">
+        <v>-4.3</v>
+      </c>
+      <c r="O247" s="2" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" s="1" t="inlineStr">
+        <is>
+          <t>102710</t>
+        </is>
+      </c>
+      <c r="B248" s="2" t="inlineStr">
+        <is>
+          <t>이엔에프테크놀로지</t>
+        </is>
+      </c>
+      <c r="C248" s="3" t="n">
+        <v>50400</v>
+      </c>
+      <c r="D248" s="3" t="n">
+        <v>116916.82</v>
+      </c>
+      <c r="E248" s="2" t="n">
+        <v>-56.89</v>
+      </c>
+      <c r="F248" s="2" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="G248" s="2" t="n">
+        <v>11.03</v>
+      </c>
+      <c r="H248" s="2" t="n">
+        <v>12.86</v>
+      </c>
+      <c r="I248" s="2" t="n">
+        <v>51.42</v>
+      </c>
+      <c r="J248" s="2" t="n">
+        <v>17.67</v>
+      </c>
+      <c r="K248" s="2" t="n">
+        <v>31.03</v>
+      </c>
+      <c r="L248" s="2" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="M248" s="2" t="inlineStr">
+        <is>
+          <t>저평가</t>
+        </is>
+      </c>
+      <c r="N248" s="4" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="O248" s="4" t="n">
+        <v>-7.14</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="1" t="inlineStr">
+        <is>
+          <t>005180</t>
+        </is>
+      </c>
+      <c r="B249" s="2" t="inlineStr">
+        <is>
+          <t>빙그레</t>
+        </is>
+      </c>
+      <c r="C249" s="3" t="n">
+        <v>73900</v>
+      </c>
+      <c r="D249" s="3" t="n">
+        <v>199703.78</v>
+      </c>
+      <c r="E249" s="2" t="n">
+        <v>-63</v>
+      </c>
+      <c r="F249" s="2" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="G249" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="H249" s="2" t="n">
+        <v>10.87</v>
+      </c>
+      <c r="I249" s="2" t="n">
+        <v>25.79</v>
+      </c>
+      <c r="J249" s="2" t="n">
+        <v>9.07</v>
+      </c>
+      <c r="K249" s="2" t="n">
+        <v>14.72</v>
+      </c>
+      <c r="L249" s="2" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="M249" s="2" t="inlineStr">
+        <is>
+          <t>저평가</t>
+        </is>
+      </c>
+      <c r="N249" s="4" t="n">
+        <v>-11.11</v>
+      </c>
+      <c r="O249" s="4" t="n">
+        <v>-31.43</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="1" t="inlineStr">
+        <is>
+          <t>112040</t>
+        </is>
+      </c>
+      <c r="B250" s="2" t="inlineStr">
+        <is>
+          <t>위메이드</t>
+        </is>
+      </c>
+      <c r="C250" s="3" t="n">
+        <v>20700</v>
+      </c>
+      <c r="D250" s="3" t="n">
+        <v>89714.14</v>
+      </c>
+      <c r="E250" s="2" t="n">
+        <v>-76.93000000000001</v>
+      </c>
+      <c r="F250" s="2" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="G250" s="2" t="n">
+        <v>11.88</v>
+      </c>
+      <c r="H250" s="2" t="n">
+        <v>13.37</v>
+      </c>
+      <c r="I250" s="2" t="n">
+        <v>37.28</v>
+      </c>
+      <c r="J250" s="2" t="n">
+        <v>17.02</v>
+      </c>
+      <c r="K250" s="2" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="L250" s="2" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="M250" s="2" t="inlineStr">
+        <is>
+          <t>저평가</t>
+        </is>
+      </c>
+      <c r="N250" s="4" t="n">
+        <v>50.7</v>
+      </c>
+      <c r="O250" s="2" t="inlineStr"/>
+    </row>
+    <row r="251">
+      <c r="A251" s="5" t="inlineStr">
+        <is>
+          <t>200710</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>에이디테크놀로지</t>
+        </is>
+      </c>
+      <c r="C251" s="6" t="n">
+        <v>51300</v>
+      </c>
+      <c r="D251" s="6" t="n">
+        <v>28521.08</v>
+      </c>
+      <c r="E251" t="n">
+        <v>79.87</v>
+      </c>
+      <c r="F251" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="G251" t="n">
+        <v>36.26</v>
+      </c>
+      <c r="H251" t="n">
+        <v>13.05</v>
+      </c>
+      <c r="I251" t="n">
+        <v>77.17</v>
+      </c>
+      <c r="J251" t="n">
+        <v>20.61</v>
+      </c>
+      <c r="K251" t="n">
+        <v>50.11</v>
+      </c>
+      <c r="L251" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t>고평가</t>
+        </is>
+      </c>
+      <c r="N251" t="inlineStr"/>
+      <c r="O251" s="7" t="n">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="1" t="inlineStr">
+        <is>
+          <t>475960</t>
+        </is>
+      </c>
+      <c r="B252" s="2" t="inlineStr">
+        <is>
+          <t>토모큐브</t>
+        </is>
+      </c>
+      <c r="C252" s="3" t="n">
+        <v>51500</v>
+      </c>
+      <c r="D252" s="3" t="n">
+        <v>87835.24000000001</v>
+      </c>
+      <c r="E252" s="2" t="n">
+        <v>-41.37</v>
+      </c>
+      <c r="F252" s="2" t="n">
+        <v>16.71</v>
+      </c>
+      <c r="G252" s="2" t="n">
+        <v>238.95</v>
+      </c>
+      <c r="H252" s="2" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="I252" s="2" t="n">
+        <v>373.68</v>
+      </c>
+      <c r="J252" s="2" t="n">
+        <v>33.08</v>
+      </c>
+      <c r="K252" s="2" t="n">
+        <v>299.86</v>
+      </c>
+      <c r="L252" s="2" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="M252" s="2" t="inlineStr">
+        <is>
+          <t>저평가</t>
+        </is>
+      </c>
+      <c r="N252" s="2" t="inlineStr"/>
+      <c r="O252" s="2" t="inlineStr"/>
+    </row>
+    <row r="253">
+      <c r="A253" s="1" t="inlineStr">
+        <is>
+          <t>060250</t>
+        </is>
+      </c>
+      <c r="B253" s="2" t="inlineStr">
+        <is>
+          <t>NHN KCP</t>
+        </is>
+      </c>
+      <c r="C253" s="3" t="n">
+        <v>17020</v>
+      </c>
+      <c r="D253" s="3" t="n">
+        <v>26081.67</v>
+      </c>
+      <c r="E253" s="2" t="n">
+        <v>-34.74</v>
+      </c>
+      <c r="F253" s="2" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="G253" s="2" t="n">
+        <v>12.14</v>
+      </c>
+      <c r="H253" s="2" t="n">
+        <v>17.01</v>
+      </c>
+      <c r="I253" s="2" t="n">
+        <v>10.81</v>
+      </c>
+      <c r="J253" s="2" t="n">
+        <v>13.15</v>
+      </c>
+      <c r="K253" s="2" t="n">
+        <v>-4.23</v>
+      </c>
+      <c r="L253" s="2" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="M253" s="2" t="inlineStr">
+        <is>
+          <t>저평가</t>
+        </is>
+      </c>
+      <c r="N253" s="4" t="n">
+        <v>24.89</v>
+      </c>
+      <c r="O253" s="4" t="n">
+        <v>344.72</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="5" t="inlineStr">
+        <is>
+          <t>425420</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>티에프이</t>
+        </is>
+      </c>
+      <c r="C254" s="6" t="n">
+        <v>56500</v>
+      </c>
+      <c r="D254" s="6" t="n">
+        <v>47521.26</v>
+      </c>
+      <c r="E254" t="n">
+        <v>18.89</v>
+      </c>
+      <c r="F254" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="G254" t="n">
+        <v>19.73</v>
+      </c>
+      <c r="H254" t="n">
+        <v>27.36</v>
+      </c>
+      <c r="I254" t="n">
+        <v>26.11</v>
+      </c>
+      <c r="J254" t="n">
+        <v>31.82</v>
+      </c>
+      <c r="K254" t="n">
+        <v>-1.43</v>
+      </c>
+      <c r="L254" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="M254" t="inlineStr">
+        <is>
+          <t>고평가</t>
+        </is>
+      </c>
+      <c r="N254" s="7" t="n">
+        <v>334.09</v>
+      </c>
+      <c r="O254" t="inlineStr"/>
+    </row>
+    <row r="255">
+      <c r="A255" s="1" t="inlineStr">
+        <is>
+          <t>005810</t>
+        </is>
+      </c>
+      <c r="B255" s="2" t="inlineStr">
+        <is>
+          <t>풍산홀딩스</t>
+        </is>
+      </c>
+      <c r="C255" s="3" t="n">
+        <v>46350</v>
+      </c>
+      <c r="D255" s="3" t="n">
+        <v>56992.44</v>
+      </c>
+      <c r="E255" s="2" t="n">
+        <v>-18.67</v>
+      </c>
+      <c r="F255" s="2" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="G255" s="2" t="n">
+        <v>10.66</v>
+      </c>
+      <c r="H255" s="2" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="I255" s="2" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="J255" s="2" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="K255" s="2" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="L255" s="2" t="inlineStr"/>
+      <c r="M255" s="2" t="inlineStr">
+        <is>
+          <t>저평가</t>
+        </is>
+      </c>
+      <c r="N255" s="4" t="n">
+        <v>11.18</v>
+      </c>
+      <c r="O255" s="2" t="inlineStr"/>
+    </row>
+    <row r="256">
+      <c r="A256" s="1" t="inlineStr">
+        <is>
+          <t>058650</t>
+        </is>
+      </c>
+      <c r="B256" s="2" t="inlineStr">
+        <is>
+          <t>세아홀딩스</t>
+        </is>
+      </c>
+      <c r="C256" s="3" t="n">
+        <v>154900</v>
+      </c>
+      <c r="D256" s="3" t="n">
+        <v>545039.75</v>
+      </c>
+      <c r="E256" s="2" t="n">
+        <v>-71.58</v>
+      </c>
+      <c r="F256" s="2" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="G256" s="2" t="n">
+        <v>8.789999999999999</v>
+      </c>
+      <c r="H256" s="2" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="I256" s="2" t="n">
+        <v>44.31</v>
+      </c>
+      <c r="J256" s="2" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K256" s="2" t="n">
+        <v>40.71</v>
+      </c>
+      <c r="L256" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M256" s="2" t="inlineStr">
+        <is>
+          <t>저평가</t>
+        </is>
+      </c>
+      <c r="N256" s="4" t="n">
+        <v>76.92</v>
+      </c>
+      <c r="O256" s="4" t="n">
+        <v>225.6</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="5" t="inlineStr">
+        <is>
+          <t>001820</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>삼화콘덴서</t>
+        </is>
+      </c>
+      <c r="C257" s="6" t="n">
+        <v>63100</v>
+      </c>
+      <c r="D257" s="6" t="n">
+        <v>42343.72</v>
+      </c>
+      <c r="E257" t="n">
+        <v>49.02</v>
+      </c>
+      <c r="F257" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="G257" t="n">
+        <v>28.91</v>
+      </c>
+      <c r="H257" t="n">
+        <v>7.32</v>
+      </c>
+      <c r="I257" t="n">
+        <v>33.37</v>
+      </c>
+      <c r="J257" t="n">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="K257" t="n">
+        <v>24.04</v>
+      </c>
+      <c r="L257" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="M257" t="inlineStr">
+        <is>
+          <t>고평가</t>
+        </is>
+      </c>
+      <c r="N257" s="7" t="n">
+        <v>-27.53</v>
+      </c>
+      <c r="O257" t="inlineStr"/>
+    </row>
+    <row r="258">
+      <c r="A258" s="1" t="inlineStr">
+        <is>
+          <t>017940</t>
+        </is>
+      </c>
+      <c r="B258" s="2" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+      <c r="C258" s="3" t="n">
+        <v>95200</v>
+      </c>
+      <c r="D258" s="3" t="n">
+        <v>324380.11</v>
+      </c>
+      <c r="E258" s="2" t="n">
+        <v>-70.65000000000001</v>
+      </c>
+      <c r="F258" s="2" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="G258" s="2" t="n">
+        <v>6.46</v>
+      </c>
+      <c r="H258" s="2" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="I258" s="2" t="n">
+        <v>88.48</v>
+      </c>
+      <c r="J258" s="2" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="K258" s="2" t="n">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="L258" s="2" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="M258" s="2" t="inlineStr">
+        <is>
+          <t>저평가</t>
+        </is>
+      </c>
+      <c r="N258" s="4" t="n">
+        <v>45.08</v>
+      </c>
+      <c r="O258" s="2" t="inlineStr"/>
+    </row>
+    <row r="259">
+      <c r="A259" s="1" t="inlineStr">
+        <is>
+          <t>336570</t>
+        </is>
+      </c>
+      <c r="B259" s="2" t="inlineStr">
+        <is>
+          <t>원텍</t>
+        </is>
+      </c>
+      <c r="C259" s="3" t="n">
+        <v>7160</v>
+      </c>
+      <c r="D259" s="3" t="n">
+        <v>51009.17</v>
+      </c>
+      <c r="E259" s="2" t="n">
+        <v>-85.95999999999999</v>
+      </c>
+      <c r="F259" s="2" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="G259" s="2" t="n">
+        <v>12.68</v>
+      </c>
+      <c r="H259" s="2" t="n">
+        <v>27.48</v>
+      </c>
+      <c r="I259" s="2" t="n">
+        <v>22.36</v>
+      </c>
+      <c r="J259" s="2" t="n">
+        <v>26.48</v>
+      </c>
+      <c r="K259" s="2" t="n">
+        <v>-5.57</v>
+      </c>
+      <c r="L259" s="2" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="M259" s="2" t="inlineStr">
+        <is>
+          <t>저평가</t>
+        </is>
+      </c>
+      <c r="N259" s="4" t="n">
+        <v>48.56</v>
+      </c>
+      <c r="O259" s="4" t="n">
+        <v>240.13</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="1" t="inlineStr">
+        <is>
+          <t>039130</t>
+        </is>
+      </c>
+      <c r="B260" s="2" t="inlineStr">
+        <is>
+          <t>하나투어</t>
+        </is>
+      </c>
+      <c r="C260" s="3" t="n">
+        <v>41200</v>
+      </c>
+      <c r="D260" s="3" t="n">
+        <v>50380.56</v>
+      </c>
+      <c r="E260" s="2" t="n">
+        <v>-18.22</v>
+      </c>
+      <c r="F260" s="2" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="G260" s="2" t="n">
+        <v>11.05</v>
+      </c>
+      <c r="H260" s="2" t="n">
+        <v>32.51</v>
+      </c>
+      <c r="I260" s="2" t="n">
+        <v>11.86</v>
+      </c>
+      <c r="J260" s="2" t="n">
+        <v>15.71</v>
+      </c>
+      <c r="K260" s="2" t="n">
+        <v>-11.75</v>
+      </c>
+      <c r="L260" s="2" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="M260" s="2" t="inlineStr">
+        <is>
+          <t>저평가</t>
+        </is>
+      </c>
+      <c r="N260" s="4" t="n">
+        <v>13.16</v>
+      </c>
+      <c r="O260" s="4" t="n">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="1" t="inlineStr">
+        <is>
+          <t>000640</t>
+        </is>
+      </c>
+      <c r="B261" s="2" t="inlineStr">
+        <is>
+          <t>동아쏘시오홀딩스</t>
+        </is>
+      </c>
+      <c r="C261" s="3" t="n">
+        <v>95000</v>
+      </c>
+      <c r="D261" s="3" t="n">
+        <v>125888.52</v>
+      </c>
+      <c r="E261" s="2" t="n">
+        <v>-24.54</v>
+      </c>
+      <c r="F261" s="2" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="G261" s="2" t="n">
+        <v>7.38</v>
+      </c>
+      <c r="H261" s="2" t="n">
+        <v>7.31</v>
+      </c>
+      <c r="I261" s="2" t="n">
+        <v>-7.4</v>
+      </c>
+      <c r="J261" s="2" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="K261" s="2" t="n">
+        <v>-11.76</v>
+      </c>
+      <c r="L261" s="2" t="inlineStr"/>
+      <c r="M261" s="2" t="inlineStr">
+        <is>
+          <t>저평가</t>
+        </is>
+      </c>
+      <c r="N261" s="4" t="n">
+        <v>19.12</v>
+      </c>
+      <c r="O261" s="4" t="n">
+        <v>255.64</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="1" t="inlineStr">
+        <is>
+          <t>053610</t>
+        </is>
+      </c>
+      <c r="B262" s="2" t="inlineStr">
+        <is>
+          <t>프로텍</t>
+        </is>
+      </c>
+      <c r="C262" s="3" t="n">
+        <v>55300</v>
+      </c>
+      <c r="D262" s="3" t="n">
+        <v>112097.75</v>
+      </c>
+      <c r="E262" s="2" t="n">
+        <v>-50.67</v>
+      </c>
+      <c r="F262" s="2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G262" s="2" t="n">
+        <v>13.84</v>
+      </c>
+      <c r="H262" s="2" t="n">
+        <v>11.55</v>
+      </c>
+      <c r="I262" s="2" t="n">
+        <v>19.35</v>
+      </c>
+      <c r="J262" s="2" t="n">
+        <v>12.63</v>
+      </c>
+      <c r="K262" s="2" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="L262" s="2" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="M262" s="2" t="inlineStr">
+        <is>
+          <t>저평가</t>
+        </is>
+      </c>
+      <c r="N262" s="4" t="n">
+        <v>245.52</v>
+      </c>
+      <c r="O262" s="2" t="inlineStr"/>
+    </row>
+    <row r="263">
+      <c r="A263" s="1" t="inlineStr">
+        <is>
+          <t>458870</t>
+        </is>
+      </c>
+      <c r="B263" s="2" t="inlineStr">
+        <is>
+          <t>씨어스테크놀로지</t>
+        </is>
+      </c>
+      <c r="C263" s="3" t="n">
+        <v>46250</v>
+      </c>
+      <c r="D263" s="3" t="n">
+        <v>132320.98</v>
+      </c>
+      <c r="E263" s="2" t="n">
+        <v>-65.05</v>
+      </c>
+      <c r="F263" s="2" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="G263" s="2" t="n">
+        <v>38.43</v>
+      </c>
+      <c r="H263" s="2" t="n">
+        <v>71.87</v>
+      </c>
+      <c r="I263" s="2" t="n">
+        <v>42.59</v>
+      </c>
+      <c r="J263" s="2" t="n">
+        <v>74.94</v>
+      </c>
+      <c r="K263" s="2" t="n">
+        <v>-24.14</v>
+      </c>
+      <c r="L263" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="M263" s="2" t="inlineStr">
+        <is>
+          <t>저평가</t>
+        </is>
+      </c>
+      <c r="N263" s="2" t="inlineStr"/>
+      <c r="O263" s="2" t="inlineStr"/>
+    </row>
+    <row r="264">
+      <c r="A264" s="5" t="inlineStr">
+        <is>
+          <t>033640</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>네패스</t>
+        </is>
+      </c>
+      <c r="C264" s="6" t="n">
+        <v>25150</v>
+      </c>
+      <c r="D264" s="6" t="n">
+        <v>13300.71</v>
+      </c>
+      <c r="E264" t="n">
+        <v>89.09</v>
+      </c>
+      <c r="F264" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="G264" t="n">
+        <v>32.35</v>
+      </c>
+      <c r="H264" t="n">
+        <v>12.11</v>
+      </c>
+      <c r="I264" t="n">
+        <v>80.12</v>
+      </c>
+      <c r="J264" t="n">
+        <v>21.05</v>
+      </c>
+      <c r="K264" t="n">
+        <v>57.31</v>
+      </c>
+      <c r="L264" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M264" t="inlineStr">
+        <is>
+          <t>고평가</t>
+        </is>
+      </c>
+      <c r="N264" s="7" t="n">
+        <v>600</v>
+      </c>
+      <c r="O264" t="inlineStr"/>
+    </row>
+    <row r="265">
+      <c r="A265" s="1" t="inlineStr">
+        <is>
+          <t>099190</t>
+        </is>
+      </c>
+      <c r="B265" s="2" t="inlineStr">
+        <is>
+          <t>아이센스</t>
+        </is>
+      </c>
+      <c r="C265" s="3" t="n">
+        <v>19890</v>
+      </c>
+      <c r="D265" s="3" t="n">
+        <v>26779.18</v>
+      </c>
+      <c r="E265" s="2" t="n">
+        <v>-25.73</v>
+      </c>
+      <c r="F265" s="2" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="G265" s="2" t="n">
+        <v>717.87</v>
+      </c>
+      <c r="H265" s="2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I265" s="2" t="n">
+        <v>989.29</v>
+      </c>
+      <c r="J265" s="2" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="K265" s="2" t="n">
+        <v>996</v>
+      </c>
+      <c r="L265" s="2" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="M265" s="2" t="inlineStr">
+        <is>
+          <t>저평가</t>
+        </is>
+      </c>
+      <c r="N265" s="4" t="n">
+        <v>192.59</v>
+      </c>
+      <c r="O265" s="2" t="inlineStr"/>
+    </row>
+    <row r="266">
+      <c r="A266" s="1" t="inlineStr">
+        <is>
+          <t>016380</t>
+        </is>
+      </c>
+      <c r="B266" s="2" t="inlineStr">
+        <is>
+          <t>KG스틸</t>
+        </is>
+      </c>
+      <c r="C266" s="3" t="n">
+        <v>5660</v>
+      </c>
+      <c r="D266" s="3" t="n">
+        <v>27623.06</v>
+      </c>
+      <c r="E266" s="2" t="n">
+        <v>-79.51000000000001</v>
+      </c>
+      <c r="F266" s="2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G266" s="2" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="H266" s="2" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="I266" s="2" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="J266" s="2" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="K266" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="L266" s="2" t="inlineStr"/>
+      <c r="M266" s="2" t="inlineStr">
+        <is>
+          <t>저평가</t>
+        </is>
+      </c>
+      <c r="N266" s="4" t="n">
+        <v>-49.54</v>
+      </c>
+      <c r="O266" s="2" t="inlineStr"/>
+    </row>
+    <row r="267">
+      <c r="A267" s="1" t="inlineStr">
+        <is>
+          <t>014830</t>
+        </is>
+      </c>
+      <c r="B267" s="2" t="inlineStr">
+        <is>
+          <t>유니드</t>
+        </is>
+      </c>
+      <c r="C267" s="3" t="n">
+        <v>81900</v>
+      </c>
+      <c r="D267" s="3" t="n">
+        <v>153898.83</v>
+      </c>
+      <c r="E267" s="2" t="n">
+        <v>-46.78</v>
+      </c>
+      <c r="F267" s="2" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="G267" s="2" t="n">
+        <v>6.62</v>
+      </c>
+      <c r="H267" s="2" t="n">
+        <v>7.56</v>
+      </c>
+      <c r="I267" s="2" t="n">
+        <v>15.24</v>
+      </c>
+      <c r="J267" s="2" t="n">
+        <v>7.29</v>
+      </c>
+      <c r="K267" s="2" t="n">
+        <v>8.99</v>
+      </c>
+      <c r="L267" s="2" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="M267" s="2" t="inlineStr">
+        <is>
+          <t>저평가</t>
+        </is>
+      </c>
+      <c r="N267" s="4" t="n">
+        <v>-8.710000000000001</v>
+      </c>
+      <c r="O267" s="4" t="n">
+        <v>-7.09</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="1" t="inlineStr">
+        <is>
+          <t>251970</t>
+        </is>
+      </c>
+      <c r="B268" s="2" t="inlineStr">
+        <is>
+          <t>펌텍코리아</t>
+        </is>
+      </c>
+      <c r="C268" s="3" t="n">
+        <v>44100</v>
+      </c>
+      <c r="D268" s="3" t="n">
+        <v>68605.71000000001</v>
+      </c>
+      <c r="E268" s="2" t="n">
+        <v>-35.72</v>
+      </c>
+      <c r="F268" s="2" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="G268" s="2" t="n">
+        <v>11.85</v>
+      </c>
+      <c r="H268" s="2" t="n">
+        <v>14.65</v>
+      </c>
+      <c r="I268" s="2" t="n">
+        <v>12.57</v>
+      </c>
+      <c r="J268" s="2" t="n">
+        <v>12.42</v>
+      </c>
+      <c r="K268" s="2" t="n">
+        <v>-1.09</v>
+      </c>
+      <c r="L268" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="M268" s="2" t="inlineStr">
+        <is>
+          <t>저평가</t>
+        </is>
+      </c>
+      <c r="N268" s="4" t="n">
+        <v>16.74</v>
+      </c>
+      <c r="O268" s="4" t="n">
+        <v>228.49</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="1" t="inlineStr">
+        <is>
+          <t>018290</t>
+        </is>
+      </c>
+      <c r="B269" s="2" t="inlineStr">
+        <is>
+          <t>브이티</t>
+        </is>
+      </c>
+      <c r="C269" s="3" t="n">
+        <v>15650</v>
+      </c>
+      <c r="D269" s="3" t="n">
+        <v>33315.83</v>
+      </c>
+      <c r="E269" s="2" t="n">
+        <v>-53.03</v>
+      </c>
+      <c r="F269" s="2" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="G269" s="2" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="H269" s="2" t="n">
+        <v>18.62</v>
+      </c>
+      <c r="I269" s="2" t="n">
+        <v>24.52</v>
+      </c>
+      <c r="J269" s="2" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="K269" s="2" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="L269" s="2" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="M269" s="2" t="inlineStr">
+        <is>
+          <t>저평가</t>
+        </is>
+      </c>
+      <c r="N269" s="4" t="n">
+        <v>-25.25</v>
+      </c>
+      <c r="O269" s="2" t="inlineStr"/>
+    </row>
+    <row r="270">
+      <c r="A270" s="1" t="inlineStr">
+        <is>
+          <t>104830</t>
+        </is>
+      </c>
+      <c r="B270" s="2" t="inlineStr">
+        <is>
+          <t>원익머트리얼즈</t>
+        </is>
+      </c>
+      <c r="C270" s="3" t="n">
+        <v>42250</v>
+      </c>
+      <c r="D270" s="3" t="n">
+        <v>85307.64</v>
+      </c>
+      <c r="E270" s="2" t="n">
+        <v>-50.47</v>
+      </c>
+      <c r="F270" s="2" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="G270" s="2" t="n">
+        <v>9.529999999999999</v>
+      </c>
+      <c r="H270" s="2" t="n">
+        <v>10.17</v>
+      </c>
+      <c r="I270" s="2" t="n">
+        <v>15.56</v>
+      </c>
+      <c r="J270" s="2" t="n">
+        <v>9.06</v>
+      </c>
+      <c r="K270" s="2" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="L270" s="2" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="M270" s="2" t="inlineStr">
+        <is>
+          <t>저평가</t>
+        </is>
+      </c>
+      <c r="N270" s="4" t="n">
+        <v>8.859999999999999</v>
+      </c>
+      <c r="O270" s="4" t="n">
+        <v>240.36</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="1" t="inlineStr">
+        <is>
+          <t>020000</t>
+        </is>
+      </c>
+      <c r="B271" s="2" t="inlineStr">
+        <is>
+          <t>한섬</t>
+        </is>
+      </c>
+      <c r="C271" s="3" t="n">
+        <v>23100</v>
+      </c>
+      <c r="D271" s="3" t="n">
+        <v>36255.06</v>
+      </c>
+      <c r="E271" s="2" t="n">
+        <v>-36.28</v>
+      </c>
+      <c r="F271" s="2" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="G271" s="2" t="n">
+        <v>7.78</v>
+      </c>
+      <c r="H271" s="2" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="I271" s="2" t="n">
+        <v>17.78</v>
+      </c>
+      <c r="J271" s="2" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="K271" s="2" t="n">
+        <v>13.36</v>
+      </c>
+      <c r="L271" s="2" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="M271" s="2" t="inlineStr">
+        <is>
+          <t>저평가</t>
+        </is>
+      </c>
+      <c r="N271" s="4" t="n">
+        <v>45.41</v>
+      </c>
+      <c r="O271" s="4" t="n">
+        <v>22.39</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="1" t="inlineStr">
+        <is>
+          <t>095660</t>
+        </is>
+      </c>
+      <c r="B272" s="2" t="inlineStr">
+        <is>
+          <t>네오위즈</t>
+        </is>
+      </c>
+      <c r="C272" s="3" t="n">
+        <v>23500</v>
+      </c>
+      <c r="D272" s="3" t="n">
+        <v>77079.77</v>
+      </c>
+      <c r="E272" s="2" t="n">
+        <v>-69.51000000000001</v>
+      </c>
+      <c r="F272" s="2" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="G272" s="2" t="n">
+        <v>11.76</v>
+      </c>
+      <c r="H272" s="2" t="n">
+        <v>7.74</v>
+      </c>
+      <c r="I272" s="2" t="n">
+        <v>14.61</v>
+      </c>
+      <c r="J272" s="2" t="n">
+        <v>6.41</v>
+      </c>
+      <c r="K272" s="2" t="n">
+        <v>6.59</v>
+      </c>
+      <c r="L272" s="2" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="M272" s="2" t="inlineStr">
+        <is>
+          <t>저평가</t>
+        </is>
+      </c>
+      <c r="N272" s="4" t="n">
+        <v>82.37</v>
+      </c>
+      <c r="O272" s="4" t="n">
+        <v>395.87</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
